--- a/daten/PTE-deutsch.xlsx
+++ b/daten/PTE-deutsch.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\projekte\pse-neu\daten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{381D0A34-F5C5-433A-98CB-5A92DC056325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CE1BB0E-7B30-4820-B3CA-155EA682898B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{1F73B8A9-2FEE-4EFC-A743-7902205BC454}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="556">
   <si>
     <t>Element</t>
   </si>
@@ -1515,18 +1515,12 @@
     <t>Standard</t>
   </si>
   <si>
-    <t>SiMe&lt;sub&gt;4&gt;/sub&gt;</t>
-  </si>
-  <si>
     <t>Empfindlichkeit relativ zu &lt;sup&gt;1&lt;/sup&gt;H</t>
   </si>
   <si>
     <t>Empfindlichkeit relativ zu &lt;sup&gt;13&lt;/sup&gt;C</t>
   </si>
   <si>
-    <t>5,87*10&lt;sup&gt;3&lt;/sup&gt;</t>
-  </si>
-  <si>
     <t>Larmorfrequenz (9,39798 T)</t>
   </si>
   <si>
@@ -1536,28 +1530,246 @@
     <t>Quadrupolmoment Q [fm&lt;sup&gt;2&lt;/sup&gt;]</t>
   </si>
   <si>
-    <t>1,11*10&lt;sup&gt;-6&lt;/sup&gt;</t>
-  </si>
-  <si>
-    <t>6,52*10&lt;sup&gt;-3&lt;/sup&gt;</t>
-  </si>
-  <si>
-    <t>Linienweitenfaktor [fm&lt;sup&gt;4&lt;/sup&gt;]</t>
-  </si>
-  <si>
     <t>Me&lt;sub4&lt;/sub&gt;Si-t1</t>
+  </si>
+  <si>
+    <t>He(gas)</t>
+  </si>
+  <si>
+    <t>SiMe&lt;sub&gt;4&lt;/sub&gt;</t>
+  </si>
+  <si>
+    <t>MeNO2</t>
+  </si>
+  <si>
+    <t>CCl3F</t>
+  </si>
+  <si>
+    <t>TMS</t>
+  </si>
+  <si>
+    <t>H3PO4</t>
+  </si>
+  <si>
+    <t>Fe(CO)5</t>
+  </si>
+  <si>
+    <t>Me2Se</t>
+  </si>
+  <si>
+    <t>Y(NO3)3</t>
+  </si>
+  <si>
+    <t>Rh(acac)3</t>
+  </si>
+  <si>
+    <t>AgNO3</t>
+  </si>
+  <si>
+    <t>Me2Cd</t>
+  </si>
+  <si>
+    <t>Me4Sn</t>
+  </si>
+  <si>
+    <t>Me2Te</t>
+  </si>
+  <si>
+    <t>XeOF4</t>
+  </si>
+  <si>
+    <t>Na2WO4</t>
+  </si>
+  <si>
+    <t>OsO4</t>
+  </si>
+  <si>
+    <t>Na2PtCl6</t>
+  </si>
+  <si>
+    <t>Me2Hg</t>
+  </si>
+  <si>
+    <t>Tl(NO3)3</t>
+  </si>
+  <si>
+    <t>Me4Pb</t>
+  </si>
+  <si>
+    <t>Ír</t>
+  </si>
+  <si>
+    <t>LiCl</t>
+  </si>
+  <si>
+    <t>BeSO4</t>
+  </si>
+  <si>
+    <t>BF3,Et2O</t>
+  </si>
+  <si>
+    <t>D2O</t>
+  </si>
+  <si>
+    <t>NaCl</t>
+  </si>
+  <si>
+    <t>MgCl2</t>
+  </si>
+  <si>
+    <t>Al(NO3)3</t>
+  </si>
+  <si>
+    <t>(NH4)2SO4</t>
+  </si>
+  <si>
+    <t>KCl</t>
+  </si>
+  <si>
+    <t>CaCl2</t>
+  </si>
+  <si>
+    <t>Sc(NO3)3</t>
+  </si>
+  <si>
+    <t>TiCl4</t>
+  </si>
+  <si>
+    <t>VOCl3</t>
+  </si>
+  <si>
+    <t>K2CrO4</t>
+  </si>
+  <si>
+    <t>KMnO4</t>
+  </si>
+  <si>
+    <t>K3[Co(CN)6]</t>
+  </si>
+  <si>
+    <t>Ni(CO)4</t>
+  </si>
+  <si>
+    <t>[Cu(CH3CN)4][ClO4]</t>
+  </si>
+  <si>
+    <t>Zn(NO3)2</t>
+  </si>
+  <si>
+    <t>Ga(NO3)3</t>
+  </si>
+  <si>
+    <t>(CH3)4Ge</t>
+  </si>
+  <si>
+    <t>NaAsF6</t>
+  </si>
+  <si>
+    <t>NaBr</t>
+  </si>
+  <si>
+    <t>RbCl</t>
+  </si>
+  <si>
+    <t>SrCl2</t>
+  </si>
+  <si>
+    <t>Zr(Cp)2Cl2</t>
+  </si>
+  <si>
+    <t>K[NbCl6]</t>
+  </si>
+  <si>
+    <t>Na2MoO4</t>
+  </si>
+  <si>
+    <t>K4[Ru(CN)6]</t>
+  </si>
+  <si>
+    <t>[Ru(CN)6]4-</t>
+  </si>
+  <si>
+    <t>K2PdCl6</t>
+  </si>
+  <si>
+    <t>In(NO3)3</t>
+  </si>
+  <si>
+    <t>KSbCl6</t>
+  </si>
+  <si>
+    <t>KI</t>
+  </si>
+  <si>
+    <t>CsNO3</t>
+  </si>
+  <si>
+    <t>BaCl2</t>
+  </si>
+  <si>
+    <t>LaCl3</t>
+  </si>
+  <si>
+    <t>Not Given</t>
+  </si>
+  <si>
+    <t>KTaCl6</t>
+  </si>
+  <si>
+    <t>KReO4</t>
+  </si>
+  <si>
+    <t>Bi(NO3)3</t>
+  </si>
+  <si>
+    <t>Linienbreitenfaktor [fm&lt;sup&gt;4&lt;/sup&gt;]</t>
+  </si>
+  <si>
+    <t>1/2</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>3/2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>5/2</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>7/2</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>9/2</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>7</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.0000"/>
-    <numFmt numFmtId="171" formatCode="0.00000000"/>
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.00000000"/>
+    <numFmt numFmtId="167" formatCode="0.0000000000"/>
+    <numFmt numFmtId="170" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1696,6 +1908,18 @@
       <vertAlign val="superscript"/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2042,17 +2266,33 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="12" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="12" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20 % - Akzent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -12831,20 +13071,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{087BCF4E-DE7D-4F29-86D7-914EDFB6372E}">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N120"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" customWidth="1"/>
-    <col min="4" max="4" width="23.5703125" customWidth="1"/>
-    <col min="5" max="5" width="19" style="4" customWidth="1"/>
-    <col min="6" max="6" width="26.42578125" style="7" customWidth="1"/>
-    <col min="7" max="7" width="79.5703125" style="7" customWidth="1"/>
-    <col min="8" max="8" width="42.7109375" customWidth="1"/>
-    <col min="9" max="9" width="40" customWidth="1"/>
-    <col min="10" max="10" width="40.140625" customWidth="1"/>
-    <col min="11" max="11" width="42.28515625" customWidth="1"/>
-    <col min="12" max="12" width="26.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="39.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" customWidth="1"/>
+    <col min="2" max="2" width="7.140625" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" style="8" customWidth="1"/>
+    <col min="5" max="5" width="19" style="19" customWidth="1"/>
+    <col min="6" max="6" width="26.42578125" style="16" customWidth="1"/>
+    <col min="7" max="7" width="29.85546875" style="7" customWidth="1"/>
+    <col min="8" max="8" width="26.85546875" style="13" customWidth="1"/>
+    <col min="9" max="9" width="20.5703125" customWidth="1"/>
+    <col min="10" max="10" width="26.85546875" customWidth="1"/>
+    <col min="11" max="11" width="25.7109375" customWidth="1"/>
+    <col min="12" max="12" width="26.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.28515625" customWidth="1"/>
     <col min="14" max="14" width="42.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -12858,38 +13100,38 @@
       <c r="C1" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="9" t="s">
         <v>469</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="18" t="s">
         <v>470</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="15" t="s">
         <v>472</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="6" t="s">
         <v>471</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="11" t="s">
         <v>473</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>474</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="5" t="s">
         <v>477</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="M1" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>481</v>
-      </c>
       <c r="N1" s="2" t="s">
-        <v>484</v>
+        <v>544</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -12902,31 +13144,31 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="8">
         <v>99.988500000000002</v>
       </c>
-      <c r="E2" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="F2" s="7">
+      <c r="E2" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F2" s="16">
         <v>4.8373535700000003</v>
       </c>
       <c r="G2" s="7">
         <v>26.752212799999999</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="12">
         <v>100</v>
       </c>
       <c r="I2" t="s">
-        <v>475</v>
-      </c>
-      <c r="J2" s="5">
-        <v>1</v>
-      </c>
-      <c r="K2" t="s">
-        <v>478</v>
-      </c>
-      <c r="L2" s="6">
+        <v>482</v>
+      </c>
+      <c r="J2" s="3">
+        <v>1</v>
+      </c>
+      <c r="K2" s="10">
+        <v>5870</v>
+      </c>
+      <c r="L2" s="4">
         <v>400.13</v>
       </c>
     </row>
@@ -12940,31 +13182,31 @@
       <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="8">
         <v>1.15E-2</v>
       </c>
-      <c r="E3" s="4">
-        <v>1</v>
-      </c>
-      <c r="F3" s="7">
+      <c r="E3" s="19">
+        <v>1</v>
+      </c>
+      <c r="F3" s="16">
         <v>1.2126007700000001</v>
       </c>
       <c r="G3" s="7">
         <v>4.1066279100000003</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="13">
         <v>15.350609</v>
       </c>
       <c r="I3" t="s">
-        <v>480</v>
-      </c>
-      <c r="J3" t="s">
-        <v>482</v>
-      </c>
-      <c r="K3" t="s">
-        <v>483</v>
-      </c>
-      <c r="L3" s="6">
+        <v>478</v>
+      </c>
+      <c r="J3" s="10">
+        <v>1.11E-6</v>
+      </c>
+      <c r="K3" s="10">
+        <v>6.5199999999999998E-3</v>
+      </c>
+      <c r="L3" s="4">
         <v>61.421999999999997</v>
       </c>
       <c r="M3">
@@ -12984,26 +13226,4723 @@
       <c r="C4">
         <v>3</v>
       </c>
-      <c r="E4" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="F4" s="7">
+      <c r="E4" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F4" s="16">
         <v>5.1597143670000003</v>
       </c>
       <c r="G4" s="7">
         <v>28.534977900000001</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="13">
         <v>106.663974</v>
       </c>
       <c r="I4" t="s">
+        <v>480</v>
+      </c>
+      <c r="L4" s="4">
+        <v>426.79500000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5" s="8">
+        <v>1.37E-4</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F5" s="17">
+        <v>-3.6851543360000001</v>
+      </c>
+      <c r="G5" s="7">
+        <v>-20.380158699999999</v>
+      </c>
+      <c r="H5" s="13">
+        <v>76.179436999999993</v>
+      </c>
+      <c r="I5" t="s">
+        <v>481</v>
+      </c>
+      <c r="J5" s="10">
+        <v>6.06E-7</v>
+      </c>
+      <c r="K5" s="10">
+        <v>3.5599999999999998E-3</v>
+      </c>
+      <c r="L5" s="4">
+        <v>304.815</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6" s="8">
+        <v>7.59</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>546</v>
+      </c>
+      <c r="F6" s="16">
+        <v>1.1625637</v>
+      </c>
+      <c r="G6" s="7">
+        <v>3.9371708999999999</v>
+      </c>
+      <c r="H6" s="13">
+        <v>14.716086000000001</v>
+      </c>
+      <c r="I6" t="s">
+        <v>503</v>
+      </c>
+      <c r="J6" s="10">
+        <v>6.4499999999999996E-4</v>
+      </c>
+      <c r="K6">
+        <v>3.79</v>
+      </c>
+      <c r="L6" s="4">
+        <v>58.883000000000003</v>
+      </c>
+      <c r="M6">
+        <v>-8.0799999999999997E-2</v>
+      </c>
+      <c r="N6">
+        <v>3.3000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>7</v>
+      </c>
+      <c r="D7" s="8">
+        <v>92.41</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F7" s="16">
+        <v>4.2040750500000001</v>
+      </c>
+      <c r="G7" s="7">
+        <v>10.3977013</v>
+      </c>
+      <c r="H7" s="13">
+        <v>38.863796999999998</v>
+      </c>
+      <c r="I7" t="s">
+        <v>503</v>
+      </c>
+      <c r="J7">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="K7" s="10">
+        <v>1590</v>
+      </c>
+      <c r="L7" s="4">
+        <v>155.506</v>
+      </c>
+      <c r="M7">
+        <v>-4.01</v>
+      </c>
+      <c r="N7">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>9</v>
+      </c>
+      <c r="D8" s="8">
+        <v>100</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F8" s="16">
+        <v>-1.5201359999999999</v>
+      </c>
+      <c r="G8" s="7">
+        <v>-3.7596660000000002</v>
+      </c>
+      <c r="H8" s="13">
+        <v>14.051812999999999</v>
+      </c>
+      <c r="I8" t="s">
+        <v>504</v>
+      </c>
+      <c r="J8" s="10">
+        <v>1.3899999999999999E-2</v>
+      </c>
+      <c r="K8">
+        <v>81.5</v>
+      </c>
+      <c r="L8" s="4">
+        <v>56.225999999999999</v>
+      </c>
+      <c r="M8">
+        <v>5.2880000000000003</v>
+      </c>
+      <c r="N8">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>10</v>
+      </c>
+      <c r="D9" s="8">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>548</v>
+      </c>
+      <c r="F9" s="16">
+        <v>2.0792055</v>
+      </c>
+      <c r="G9" s="7">
+        <v>2.8746786000000002</v>
+      </c>
+      <c r="H9" s="13">
+        <v>10.743658</v>
+      </c>
+      <c r="I9" t="s">
+        <v>505</v>
+      </c>
+      <c r="J9" s="10">
+        <v>3.9500000000000004E-3</v>
+      </c>
+      <c r="K9">
+        <v>23.2</v>
+      </c>
+      <c r="L9" s="4">
+        <v>42.988999999999997</v>
+      </c>
+      <c r="M9">
+        <v>8.4589999999999996</v>
+      </c>
+      <c r="N9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10">
+        <v>11</v>
+      </c>
+      <c r="D10" s="8">
+        <v>80.099999999999994</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F10" s="16">
+        <v>3.4710307999999999</v>
+      </c>
+      <c r="G10" s="7">
+        <v>8.5847043999999997</v>
+      </c>
+      <c r="H10" s="13">
+        <v>32.083973999999998</v>
+      </c>
+      <c r="I10" t="s">
+        <v>505</v>
+      </c>
+      <c r="J10">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="K10" s="10">
+        <v>777</v>
+      </c>
+      <c r="L10" s="4">
+        <v>128.37799999999999</v>
+      </c>
+      <c r="M10">
+        <v>4.0590000000000002</v>
+      </c>
+      <c r="N10">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>13</v>
+      </c>
+      <c r="D11" s="8">
+        <v>1.07</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F11" s="16">
+        <v>1.2166129999999999</v>
+      </c>
+      <c r="G11" s="7">
+        <v>6.7282840000000004</v>
+      </c>
+      <c r="H11" s="13">
+        <v>25.145019999999999</v>
+      </c>
+      <c r="I11" t="s">
+        <v>482</v>
+      </c>
+      <c r="J11" s="10">
+        <v>1.7000000000000001E-4</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11" s="4">
+        <v>100.613</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12">
+        <v>15</v>
+      </c>
+      <c r="D12" s="8">
+        <v>0.36799999999999999</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F12" s="14">
+        <v>-0.49049746</v>
+      </c>
+      <c r="G12" s="7">
+        <v>-2.7126180400000002</v>
+      </c>
+      <c r="H12" s="14">
+        <v>10.136767000000001</v>
+      </c>
+      <c r="I12" t="s">
+        <v>483</v>
+      </c>
+      <c r="J12" s="10">
+        <v>3.8399999999999997E-6</v>
+      </c>
+      <c r="K12" s="10">
+        <v>2.2499999999999999E-2</v>
+      </c>
+      <c r="L12" s="4">
+        <v>40.56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13">
+        <v>14</v>
+      </c>
+      <c r="D13" s="8">
+        <v>99.632000000000005</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>546</v>
+      </c>
+      <c r="F13" s="16">
+        <v>0.57100428000000003</v>
+      </c>
+      <c r="G13" s="7">
+        <v>1.9337792</v>
+      </c>
+      <c r="H13" s="13">
+        <v>7.2263169999999999</v>
+      </c>
+      <c r="I13" t="s">
+        <v>483</v>
+      </c>
+      <c r="J13" s="10">
+        <v>1E-3</v>
+      </c>
+      <c r="K13">
+        <v>5.9</v>
+      </c>
+      <c r="L13" s="4">
+        <v>28.914999999999999</v>
+      </c>
+      <c r="M13">
+        <v>2.044</v>
+      </c>
+      <c r="N13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14">
+        <v>17</v>
+      </c>
+      <c r="D14" s="8">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>549</v>
+      </c>
+      <c r="F14" s="16">
+        <v>-2.2407699999999999</v>
+      </c>
+      <c r="G14" s="7">
+        <v>-3.6280800000000002</v>
+      </c>
+      <c r="H14" s="13">
+        <v>13.556457</v>
+      </c>
+      <c r="I14" t="s">
+        <v>506</v>
+      </c>
+      <c r="J14" s="10">
+        <v>1.11E-5</v>
+      </c>
+      <c r="K14" s="10">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="L14" s="4">
+        <v>54.243000000000002</v>
+      </c>
+      <c r="M14">
+        <v>-2.5579999999999998</v>
+      </c>
+      <c r="N14">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>9</v>
+      </c>
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15">
+        <v>19</v>
+      </c>
+      <c r="D15" s="8">
+        <v>100</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F15" s="14">
+        <v>4.5533330000000003</v>
+      </c>
+      <c r="G15" s="7">
+        <v>25.181480000000001</v>
+      </c>
+      <c r="H15" s="14">
+        <v>94.094010999999995</v>
+      </c>
+      <c r="I15" t="s">
+        <v>484</v>
+      </c>
+      <c r="J15">
+        <v>0.83399999999999996</v>
+      </c>
+      <c r="K15" s="10">
+        <v>4900</v>
+      </c>
+      <c r="L15" s="4">
+        <v>376.49799999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>10</v>
+      </c>
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16">
+        <v>21</v>
+      </c>
+      <c r="D16" s="8">
+        <v>0.27</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F16" s="16">
+        <v>-0.85437600000000002</v>
+      </c>
+      <c r="G16" s="7">
+        <v>-2.1130800000000001</v>
+      </c>
+      <c r="H16" s="13">
+        <v>7.8942959999999998</v>
+      </c>
+      <c r="I16" t="s">
+        <v>25</v>
+      </c>
+      <c r="J16" s="10">
+        <v>9.2699999999999993E-6</v>
+      </c>
+      <c r="K16" s="10">
+        <v>3.9100000000000003E-2</v>
+      </c>
+      <c r="L16" s="4">
+        <v>31.587</v>
+      </c>
+      <c r="M16">
+        <v>10.154999999999999</v>
+      </c>
+      <c r="N16">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>11</v>
+      </c>
+      <c r="B17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17">
+        <v>23</v>
+      </c>
+      <c r="D17" s="8">
+        <v>100</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F17" s="16">
+        <v>2.8629810999999998</v>
+      </c>
+      <c r="G17" s="7">
+        <v>7.0808492999999997</v>
+      </c>
+      <c r="H17" s="13">
+        <v>26.451899999999998</v>
+      </c>
+      <c r="I17" t="s">
+        <v>507</v>
+      </c>
+      <c r="J17" s="10">
+        <v>9.2700000000000005E-2</v>
+      </c>
+      <c r="K17" s="10">
+        <v>545</v>
+      </c>
+      <c r="L17" s="4">
+        <v>105.842</v>
+      </c>
+      <c r="M17">
+        <v>10.4</v>
+      </c>
+      <c r="N17">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18">
+        <v>25</v>
+      </c>
+      <c r="D18" s="8">
+        <v>10</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>549</v>
+      </c>
+      <c r="F18" s="16">
+        <v>-1.0122</v>
+      </c>
+      <c r="G18" s="7">
+        <v>-1.63887</v>
+      </c>
+      <c r="H18" s="13">
+        <v>6.1216350000000004</v>
+      </c>
+      <c r="I18" t="s">
+        <v>508</v>
+      </c>
+      <c r="J18" s="10">
+        <v>2.6800000000000001E-4</v>
+      </c>
+      <c r="K18">
+        <v>1.58</v>
+      </c>
+      <c r="L18" s="4">
+        <v>24.494</v>
+      </c>
+      <c r="M18">
+        <v>19.940000000000001</v>
+      </c>
+      <c r="N18">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19">
+        <v>27</v>
+      </c>
+      <c r="D19" s="8">
+        <v>100</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>549</v>
+      </c>
+      <c r="F19" s="16">
+        <v>4.3086865000000003</v>
+      </c>
+      <c r="G19" s="7">
+        <v>6.9762715000000002</v>
+      </c>
+      <c r="H19" s="13">
+        <v>26.056858999999999</v>
+      </c>
+      <c r="I19" t="s">
+        <v>509</v>
+      </c>
+      <c r="J19">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="K19" s="10">
+        <v>1220</v>
+      </c>
+      <c r="L19" s="4">
+        <v>104.261</v>
+      </c>
+      <c r="M19">
+        <v>14.66</v>
+      </c>
+      <c r="N19">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20">
+        <v>29</v>
+      </c>
+      <c r="D20" s="8">
+        <v>4.6832000000000003</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F20" s="14">
+        <v>-0.96179000000000003</v>
+      </c>
+      <c r="G20" s="7">
+        <v>-5.319</v>
+      </c>
+      <c r="H20" s="14">
+        <v>19.867187000000001</v>
+      </c>
+      <c r="I20" t="s">
         <v>485</v>
       </c>
-      <c r="L4" s="6">
-        <v>426.79500000000002</v>
+      <c r="J20" s="10">
+        <v>3.68E-4</v>
+      </c>
+      <c r="K20">
+        <v>2.16</v>
+      </c>
+      <c r="L20" s="4">
+        <v>79.495000000000005</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21">
+        <v>31</v>
+      </c>
+      <c r="D21" s="8">
+        <v>100</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F21" s="14">
+        <v>1.9599899999999999</v>
+      </c>
+      <c r="G21" s="7">
+        <v>10.839399999999999</v>
+      </c>
+      <c r="H21" s="14">
+        <v>40.480741999999999</v>
+      </c>
+      <c r="I21" t="s">
+        <v>486</v>
+      </c>
+      <c r="J21" s="10">
+        <v>6.6500000000000004E-2</v>
+      </c>
+      <c r="K21" s="10">
+        <v>391</v>
+      </c>
+      <c r="L21" s="4">
+        <v>161.976</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>16</v>
+      </c>
+      <c r="B22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22">
+        <v>33</v>
+      </c>
+      <c r="D22" s="8">
+        <v>0.76</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F22" s="16">
+        <v>0.83116959999999995</v>
+      </c>
+      <c r="G22" s="7">
+        <v>2.055685</v>
+      </c>
+      <c r="H22" s="13">
+        <v>7.6760000000000002</v>
+      </c>
+      <c r="I22" t="s">
+        <v>510</v>
+      </c>
+      <c r="J22" s="10">
+        <v>1.7200000000000001E-5</v>
+      </c>
+      <c r="K22">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="L22" s="4">
+        <v>30.713999999999999</v>
+      </c>
+      <c r="M22">
+        <v>-6.78</v>
+      </c>
+      <c r="N22">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>17</v>
+      </c>
+      <c r="B23" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23">
+        <v>35</v>
+      </c>
+      <c r="D23" s="8">
+        <v>75.78</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F23" s="16">
+        <v>1.061035</v>
+      </c>
+      <c r="G23" s="7">
+        <v>2.6241979999999998</v>
+      </c>
+      <c r="H23" s="13">
+        <v>9.7979090000000006</v>
+      </c>
+      <c r="I23" t="s">
+        <v>507</v>
+      </c>
+      <c r="J23" s="10">
+        <v>3.5799999999999998E-3</v>
+      </c>
+      <c r="K23">
+        <v>21</v>
+      </c>
+      <c r="L23" s="4">
+        <v>39.204000000000001</v>
+      </c>
+      <c r="M23">
+        <v>-8.1649999999999991</v>
+      </c>
+      <c r="N23">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>17</v>
+      </c>
+      <c r="B24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24">
+        <v>37</v>
+      </c>
+      <c r="D24" s="8">
+        <v>24.22</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F24" s="16">
+        <v>0.88319979999999998</v>
+      </c>
+      <c r="G24" s="7">
+        <v>2.1843680000000001</v>
+      </c>
+      <c r="H24" s="13">
+        <v>8.1557250000000003</v>
+      </c>
+      <c r="I24" t="s">
+        <v>507</v>
+      </c>
+      <c r="J24" s="10">
+        <v>6.5899999999999997E-4</v>
+      </c>
+      <c r="K24">
+        <v>3.87</v>
+      </c>
+      <c r="L24" s="4">
+        <v>32.634</v>
+      </c>
+      <c r="M24">
+        <v>-6.4349999999999996</v>
+      </c>
+      <c r="N24">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>19</v>
+      </c>
+      <c r="B25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25">
+        <v>39</v>
+      </c>
+      <c r="D25" s="8">
+        <v>93.258099999999999</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F25" s="16">
+        <v>0.50543375999999995</v>
+      </c>
+      <c r="G25" s="7">
+        <v>1.2500608</v>
+      </c>
+      <c r="H25" s="13">
+        <v>4.6663730000000001</v>
+      </c>
+      <c r="I25" t="s">
+        <v>511</v>
+      </c>
+      <c r="J25" s="10">
+        <v>4.7600000000000002E-4</v>
+      </c>
+      <c r="K25">
+        <v>2.79</v>
+      </c>
+      <c r="L25" s="4">
+        <v>18.672000000000001</v>
+      </c>
+      <c r="M25">
+        <v>5.85</v>
+      </c>
+      <c r="N25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>19</v>
+      </c>
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26">
+        <v>40</v>
+      </c>
+      <c r="D26" s="8">
+        <v>1.17E-2</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>550</v>
+      </c>
+      <c r="F26" s="16">
+        <v>-1.4513202999999999</v>
+      </c>
+      <c r="G26" s="7">
+        <v>-1.5542853999999999</v>
+      </c>
+      <c r="H26" s="13">
+        <v>5.8020180000000003</v>
+      </c>
+      <c r="I26" t="s">
+        <v>511</v>
+      </c>
+      <c r="J26" s="10">
+        <v>6.1200000000000003E-7</v>
+      </c>
+      <c r="K26" s="10">
+        <v>3.5899999999999999E-3</v>
+      </c>
+      <c r="M26">
+        <v>-7.3</v>
+      </c>
+      <c r="N26">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>19</v>
+      </c>
+      <c r="B27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27">
+        <v>41</v>
+      </c>
+      <c r="D27" s="8">
+        <v>6.7302</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F27" s="16">
+        <v>0.27739608999999998</v>
+      </c>
+      <c r="G27" s="7">
+        <v>0.68606807999999997</v>
+      </c>
+      <c r="H27" s="13">
+        <v>2.5613049999999999</v>
+      </c>
+      <c r="I27" t="s">
+        <v>511</v>
+      </c>
+      <c r="J27" s="10">
+        <v>5.6799999999999998E-6</v>
+      </c>
+      <c r="K27" s="10">
+        <v>3.3300000000000003E-2</v>
+      </c>
+      <c r="L27" s="4">
+        <v>10.249000000000001</v>
+      </c>
+      <c r="M27">
+        <v>7.11</v>
+      </c>
+      <c r="N27">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>20</v>
+      </c>
+      <c r="B28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28">
+        <v>43</v>
+      </c>
+      <c r="D28" s="8">
+        <v>0.13500000000000001</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>551</v>
+      </c>
+      <c r="F28" s="16">
+        <v>-1.494067</v>
+      </c>
+      <c r="G28" s="7">
+        <v>-1.803069</v>
+      </c>
+      <c r="H28" s="13">
+        <v>6.730029</v>
+      </c>
+      <c r="I28" t="s">
+        <v>512</v>
+      </c>
+      <c r="J28" s="10">
+        <v>8.6799999999999999E-6</v>
+      </c>
+      <c r="K28" s="10">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="L28" s="4">
+        <v>26.928999999999998</v>
+      </c>
+      <c r="M28">
+        <v>-4.08</v>
+      </c>
+      <c r="N28">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>21</v>
+      </c>
+      <c r="B29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29">
+        <v>45</v>
+      </c>
+      <c r="D29" s="8">
+        <v>100</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>551</v>
+      </c>
+      <c r="F29" s="16">
+        <v>5.3933489000000003</v>
+      </c>
+      <c r="G29" s="7">
+        <v>6.5087973000000003</v>
+      </c>
+      <c r="H29" s="13">
+        <v>24.291747000000001</v>
+      </c>
+      <c r="I29" t="s">
+        <v>513</v>
+      </c>
+      <c r="J29">
+        <v>0.30199999999999999</v>
+      </c>
+      <c r="K29" s="10">
+        <v>1780</v>
+      </c>
+      <c r="L29" s="4">
+        <v>97.198999999999998</v>
+      </c>
+      <c r="M29">
+        <v>-22</v>
+      </c>
+      <c r="N29">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>22</v>
+      </c>
+      <c r="B30" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30">
+        <v>47</v>
+      </c>
+      <c r="D30" s="8">
+        <v>7.44</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>549</v>
+      </c>
+      <c r="F30" s="16">
+        <v>-0.93293999999999999</v>
+      </c>
+      <c r="G30" s="7">
+        <v>-1.5105</v>
+      </c>
+      <c r="H30" s="13">
+        <v>5.6375339999999996</v>
+      </c>
+      <c r="I30" t="s">
+        <v>514</v>
+      </c>
+      <c r="J30" s="10">
+        <v>1.56E-4</v>
+      </c>
+      <c r="K30">
+        <v>0.91800000000000004</v>
+      </c>
+      <c r="L30" s="4">
+        <v>22.556999999999999</v>
+      </c>
+      <c r="M30">
+        <v>30.2</v>
+      </c>
+      <c r="N30">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>22</v>
+      </c>
+      <c r="B31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31">
+        <v>49</v>
+      </c>
+      <c r="D31" s="8">
+        <v>5.41</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>551</v>
+      </c>
+      <c r="F31" s="16">
+        <v>-1.2520100000000001</v>
+      </c>
+      <c r="G31" s="7">
+        <v>-1.51095</v>
+      </c>
+      <c r="H31" s="13">
+        <v>5.6390370000000001</v>
+      </c>
+      <c r="I31" t="s">
+        <v>514</v>
+      </c>
+      <c r="J31" s="10">
+        <v>2.05E-4</v>
+      </c>
+      <c r="K31">
+        <v>1.2</v>
+      </c>
+      <c r="L31" s="4">
+        <v>22.562999999999999</v>
+      </c>
+      <c r="M31">
+        <v>24.7</v>
+      </c>
+      <c r="N31">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>23</v>
+      </c>
+      <c r="B32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32">
+        <v>50</v>
+      </c>
+      <c r="D32" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>552</v>
+      </c>
+      <c r="F32" s="16">
+        <v>3.6137570000000001</v>
+      </c>
+      <c r="G32" s="7">
+        <v>2.6706490000000001</v>
+      </c>
+      <c r="H32" s="13">
+        <v>9.9703090000000003</v>
+      </c>
+      <c r="I32" t="s">
+        <v>515</v>
+      </c>
+      <c r="J32" s="10">
+        <v>1.3899999999999999E-4</v>
+      </c>
+      <c r="K32">
+        <v>0.81799999999999995</v>
+      </c>
+      <c r="L32" s="4">
+        <v>39.893999999999998</v>
+      </c>
+      <c r="M32">
+        <v>21</v>
+      </c>
+      <c r="N32">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>23</v>
+      </c>
+      <c r="B33" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33">
+        <v>51</v>
+      </c>
+      <c r="D33" s="8">
+        <v>99.75</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>551</v>
+      </c>
+      <c r="F33" s="16">
+        <v>5.8380834999999998</v>
+      </c>
+      <c r="G33" s="7">
+        <v>7.0455116999999996</v>
+      </c>
+      <c r="H33" s="13">
+        <v>26.302948000000001</v>
+      </c>
+      <c r="I33" t="s">
+        <v>515</v>
+      </c>
+      <c r="J33">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="K33" s="10">
+        <v>2250</v>
+      </c>
+      <c r="L33" s="4">
+        <v>105.246</v>
+      </c>
+      <c r="M33">
+        <v>-5.2</v>
+      </c>
+      <c r="N33">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>24</v>
+      </c>
+      <c r="B34" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34">
+        <v>53</v>
+      </c>
+      <c r="D34" s="8">
+        <v>9.5009999999999994</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F34" s="16">
+        <v>-0.61263000000000001</v>
+      </c>
+      <c r="G34" s="7">
+        <v>-1.5152000000000001</v>
+      </c>
+      <c r="H34" s="13">
+        <v>5.6524960000000002</v>
+      </c>
+      <c r="I34" t="s">
+        <v>516</v>
+      </c>
+      <c r="J34" s="10">
+        <v>8.6299999999999997E-5</v>
+      </c>
+      <c r="K34">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="L34" s="4">
+        <v>22.617000000000001</v>
+      </c>
+      <c r="M34">
+        <v>-15</v>
+      </c>
+      <c r="N34">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>25</v>
+      </c>
+      <c r="B35" t="s">
+        <v>55</v>
+      </c>
+      <c r="C35">
+        <v>55</v>
+      </c>
+      <c r="D35" s="8">
+        <v>100</v>
+      </c>
+      <c r="E35" s="19" t="s">
+        <v>549</v>
+      </c>
+      <c r="F35" s="16">
+        <v>4.1042436999999996</v>
+      </c>
+      <c r="G35" s="7">
+        <v>6.6452546000000003</v>
+      </c>
+      <c r="H35" s="13">
+        <v>24.789218000000002</v>
+      </c>
+      <c r="I35" t="s">
+        <v>517</v>
+      </c>
+      <c r="J35">
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="K35" s="10">
+        <v>1050</v>
+      </c>
+      <c r="L35" s="4">
+        <v>99.188999999999993</v>
+      </c>
+      <c r="M35">
+        <v>33</v>
+      </c>
+      <c r="N35">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>26</v>
+      </c>
+      <c r="B36" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36">
+        <v>57</v>
+      </c>
+      <c r="D36" s="8">
+        <v>2.1190000000000002</v>
+      </c>
+      <c r="E36" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F36" s="14">
+        <v>0.15696360000000001</v>
+      </c>
+      <c r="G36" s="7">
+        <v>0.86806240000000001</v>
+      </c>
+      <c r="H36" s="14">
+        <v>3.237778</v>
+      </c>
+      <c r="I36" t="s">
+        <v>487</v>
+      </c>
+      <c r="J36" s="10">
+        <v>7.2399999999999997E-7</v>
+      </c>
+      <c r="K36" s="10">
+        <v>4.2500000000000003E-3</v>
+      </c>
+      <c r="L36" s="4">
+        <v>12.955</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>27</v>
+      </c>
+      <c r="B37" t="s">
+        <v>59</v>
+      </c>
+      <c r="C37">
+        <v>59</v>
+      </c>
+      <c r="D37" s="8">
+        <v>100</v>
+      </c>
+      <c r="E37" s="19" t="s">
+        <v>551</v>
+      </c>
+      <c r="F37" s="16">
+        <v>5.2469999999999999</v>
+      </c>
+      <c r="G37" s="7">
+        <v>6.3319999999999999</v>
+      </c>
+      <c r="H37" s="13">
+        <v>23.727074000000002</v>
+      </c>
+      <c r="I37" t="s">
+        <v>518</v>
+      </c>
+      <c r="J37">
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="K37" s="10">
+        <v>1640</v>
+      </c>
+      <c r="L37" s="4">
+        <v>94.938999999999993</v>
+      </c>
+      <c r="M37">
+        <v>42</v>
+      </c>
+      <c r="N37">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>28</v>
+      </c>
+      <c r="B38" t="s">
+        <v>62</v>
+      </c>
+      <c r="C38">
+        <v>61</v>
+      </c>
+      <c r="D38" s="8">
+        <v>1.1398999999999999</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F38" s="16">
+        <v>-0.96826999999999996</v>
+      </c>
+      <c r="G38" s="7">
+        <v>-2.3948</v>
+      </c>
+      <c r="H38" s="13">
+        <v>8.9360510000000009</v>
+      </c>
+      <c r="I38" t="s">
+        <v>519</v>
+      </c>
+      <c r="J38" s="10">
+        <v>4.0899999999999998E-5</v>
+      </c>
+      <c r="K38">
+        <v>0.24</v>
+      </c>
+      <c r="L38" s="4">
+        <v>35.756</v>
+      </c>
+      <c r="M38">
+        <v>16.2</v>
+      </c>
+      <c r="N38">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>29</v>
+      </c>
+      <c r="B39" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39">
+        <v>63</v>
+      </c>
+      <c r="D39" s="8">
+        <v>69.17</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F39" s="16">
+        <v>2.8754908000000001</v>
+      </c>
+      <c r="G39" s="7">
+        <v>7.1117889999999999</v>
+      </c>
+      <c r="H39" s="13">
+        <v>26.515473</v>
+      </c>
+      <c r="I39" t="s">
+        <v>520</v>
+      </c>
+      <c r="J39" s="10">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="K39" s="10">
+        <v>382</v>
+      </c>
+      <c r="L39" s="4">
+        <v>106.096</v>
+      </c>
+      <c r="M39">
+        <v>-22</v>
+      </c>
+      <c r="N39">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>29</v>
+      </c>
+      <c r="B40" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40">
+        <v>65</v>
+      </c>
+      <c r="D40" s="8">
+        <v>30.83</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F40" s="16">
+        <v>3.0746500000000001</v>
+      </c>
+      <c r="G40" s="7">
+        <v>7.6043500000000002</v>
+      </c>
+      <c r="H40" s="13">
+        <v>28.403693000000001</v>
+      </c>
+      <c r="I40" t="s">
+        <v>520</v>
+      </c>
+      <c r="J40" s="10">
+        <v>3.5400000000000001E-2</v>
+      </c>
+      <c r="K40" s="10">
+        <v>208</v>
+      </c>
+      <c r="L40" s="4">
+        <v>113.652</v>
+      </c>
+      <c r="M40">
+        <v>-20.399999999999999</v>
+      </c>
+      <c r="N40">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>30</v>
+      </c>
+      <c r="B41" t="s">
+        <v>65</v>
+      </c>
+      <c r="C41">
+        <v>67</v>
+      </c>
+      <c r="D41" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E41" s="19" t="s">
+        <v>549</v>
+      </c>
+      <c r="F41" s="16">
+        <v>1.0355559999999999</v>
+      </c>
+      <c r="G41" s="7">
+        <v>1.676688</v>
+      </c>
+      <c r="H41" s="13">
+        <v>6.2568029999999997</v>
+      </c>
+      <c r="I41" t="s">
+        <v>521</v>
+      </c>
+      <c r="J41" s="10">
+        <v>1.18E-4</v>
+      </c>
+      <c r="K41">
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="L41" s="4">
+        <v>25.035</v>
+      </c>
+      <c r="M41">
+        <v>15</v>
+      </c>
+      <c r="N41">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>31</v>
+      </c>
+      <c r="B42" t="s">
+        <v>67</v>
+      </c>
+      <c r="C42">
+        <v>69</v>
+      </c>
+      <c r="D42" s="8">
+        <v>60.107999999999997</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F42" s="16">
+        <v>2.603405</v>
+      </c>
+      <c r="G42" s="7">
+        <v>6.4388550000000002</v>
+      </c>
+      <c r="H42" s="13">
+        <v>24.001353999999999</v>
+      </c>
+      <c r="I42" t="s">
+        <v>522</v>
+      </c>
+      <c r="J42" s="10">
+        <v>4.19E-2</v>
+      </c>
+      <c r="K42" s="10">
+        <v>246</v>
+      </c>
+      <c r="L42" s="4">
+        <v>96.037000000000006</v>
+      </c>
+      <c r="M42">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="N42">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>31</v>
+      </c>
+      <c r="B43" t="s">
+        <v>67</v>
+      </c>
+      <c r="C43">
+        <v>71</v>
+      </c>
+      <c r="D43" s="8">
+        <v>39.892000000000003</v>
+      </c>
+      <c r="E43" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F43" s="16">
+        <v>3.307871</v>
+      </c>
+      <c r="G43" s="7">
+        <v>8.1811710000000009</v>
+      </c>
+      <c r="H43" s="13">
+        <v>30.496704000000001</v>
+      </c>
+      <c r="I43" t="s">
+        <v>522</v>
+      </c>
+      <c r="J43" s="10">
+        <v>5.7099999999999998E-2</v>
+      </c>
+      <c r="K43" s="10">
+        <v>335</v>
+      </c>
+      <c r="L43" s="4">
+        <v>122.026</v>
+      </c>
+      <c r="M43">
+        <v>10.7</v>
+      </c>
+      <c r="N43">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>32</v>
+      </c>
+      <c r="B44" t="s">
+        <v>70</v>
+      </c>
+      <c r="C44">
+        <v>73</v>
+      </c>
+      <c r="D44" s="8">
+        <v>7.73</v>
+      </c>
+      <c r="E44" s="19" t="s">
+        <v>553</v>
+      </c>
+      <c r="F44" s="16">
+        <v>-0.97228809999999999</v>
+      </c>
+      <c r="G44" s="7">
+        <v>-0.93603029999999998</v>
+      </c>
+      <c r="H44" s="13">
+        <v>3.4883150000000001</v>
+      </c>
+      <c r="I44" t="s">
+        <v>523</v>
+      </c>
+      <c r="J44" s="10">
+        <v>1.0900000000000001E-4</v>
+      </c>
+      <c r="K44">
+        <v>0.64200000000000002</v>
+      </c>
+      <c r="L44" s="4">
+        <v>13.958</v>
+      </c>
+      <c r="M44">
+        <v>-19.600000000000001</v>
+      </c>
+      <c r="N44">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>33</v>
+      </c>
+      <c r="B45" t="s">
+        <v>72</v>
+      </c>
+      <c r="C45">
+        <v>75</v>
+      </c>
+      <c r="D45" s="8">
+        <v>100</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F45" s="16">
+        <v>1.8583540000000001</v>
+      </c>
+      <c r="G45" s="7">
+        <v>4.5961629999999998</v>
+      </c>
+      <c r="H45" s="13">
+        <v>17.122613999999999</v>
+      </c>
+      <c r="I45" t="s">
+        <v>524</v>
+      </c>
+      <c r="J45" s="10">
+        <v>2.53E-2</v>
+      </c>
+      <c r="K45" s="10">
+        <v>149</v>
+      </c>
+      <c r="L45" s="4">
+        <v>68.513000000000005</v>
+      </c>
+      <c r="M45">
+        <v>31.4</v>
+      </c>
+      <c r="N45">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>34</v>
+      </c>
+      <c r="B46" t="s">
+        <v>74</v>
+      </c>
+      <c r="C46">
+        <v>77</v>
+      </c>
+      <c r="D46" s="8">
+        <v>7.63</v>
+      </c>
+      <c r="E46" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F46" s="14">
+        <v>0.92677577</v>
+      </c>
+      <c r="G46" s="7">
+        <v>5.1253856999999998</v>
+      </c>
+      <c r="H46" s="14">
+        <v>19.071512999999999</v>
+      </c>
+      <c r="I46" t="s">
+        <v>488</v>
+      </c>
+      <c r="J46" s="10">
+        <v>5.3700000000000004E-4</v>
+      </c>
+      <c r="K46">
+        <v>3.15</v>
+      </c>
+      <c r="L46" s="4">
+        <v>76.311000000000007</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>35</v>
+      </c>
+      <c r="B47" t="s">
+        <v>75</v>
+      </c>
+      <c r="C47">
+        <v>79</v>
+      </c>
+      <c r="D47" s="8">
+        <v>50.69</v>
+      </c>
+      <c r="E47" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F47" s="16">
+        <v>2.7193510000000001</v>
+      </c>
+      <c r="G47" s="7">
+        <v>6.7256159999999996</v>
+      </c>
+      <c r="H47" s="13">
+        <v>25.053979999999999</v>
+      </c>
+      <c r="I47" t="s">
+        <v>525</v>
+      </c>
+      <c r="J47" s="10">
+        <v>7.6700000000000004E-2</v>
+      </c>
+      <c r="K47" s="10">
+        <v>451</v>
+      </c>
+      <c r="L47" s="4">
+        <v>100.248</v>
+      </c>
+      <c r="M47">
+        <v>31.3</v>
+      </c>
+      <c r="N47">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>35</v>
+      </c>
+      <c r="B48" t="s">
+        <v>75</v>
+      </c>
+      <c r="C48">
+        <v>81</v>
+      </c>
+      <c r="D48" s="8">
+        <v>49.31</v>
+      </c>
+      <c r="E48" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F48" s="16">
+        <v>2.9312830000000001</v>
+      </c>
+      <c r="G48" s="7">
+        <v>7.2497759999999998</v>
+      </c>
+      <c r="H48" s="13">
+        <v>27.006518</v>
+      </c>
+      <c r="I48" t="s">
+        <v>525</v>
+      </c>
+      <c r="J48" s="10">
+        <v>9.6500000000000002E-2</v>
+      </c>
+      <c r="K48" s="10">
+        <v>567</v>
+      </c>
+      <c r="L48" s="4">
+        <v>108.06100000000001</v>
+      </c>
+      <c r="M48">
+        <v>26.2</v>
+      </c>
+      <c r="N48">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>36</v>
+      </c>
+      <c r="B49" t="s">
+        <v>78</v>
+      </c>
+      <c r="C49">
+        <v>83</v>
+      </c>
+      <c r="D49" s="8">
+        <v>11.49</v>
+      </c>
+      <c r="E49" s="19" t="s">
+        <v>553</v>
+      </c>
+      <c r="F49" s="16">
+        <v>-1.07311</v>
+      </c>
+      <c r="G49" s="7">
+        <v>-1.0330999999999999</v>
+      </c>
+      <c r="H49" s="13">
+        <v>3.8475999999999999</v>
+      </c>
+      <c r="I49" t="s">
+        <v>78</v>
+      </c>
+      <c r="J49" s="10">
+        <v>1.9000000000000001E-4</v>
+      </c>
+      <c r="K49">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="L49" s="4">
+        <v>15.395</v>
+      </c>
+      <c r="M49">
+        <v>25.9</v>
+      </c>
+      <c r="N49">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>37</v>
+      </c>
+      <c r="B50" t="s">
+        <v>80</v>
+      </c>
+      <c r="C50">
+        <v>85</v>
+      </c>
+      <c r="D50" s="8">
+        <v>72.17</v>
+      </c>
+      <c r="E50" s="19" t="s">
+        <v>549</v>
+      </c>
+      <c r="F50" s="16">
+        <v>1.6013071000000001</v>
+      </c>
+      <c r="G50" s="7">
+        <v>2.592705</v>
+      </c>
+      <c r="H50" s="13">
+        <v>9.6549429999999994</v>
+      </c>
+      <c r="I50" t="s">
+        <v>526</v>
+      </c>
+      <c r="J50" s="10">
+        <v>7.6699999999999997E-3</v>
+      </c>
+      <c r="K50">
+        <v>45</v>
+      </c>
+      <c r="L50" s="4">
+        <v>38.631999999999998</v>
+      </c>
+      <c r="M50">
+        <v>27.6</v>
+      </c>
+      <c r="N50">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>37</v>
+      </c>
+      <c r="B51" t="s">
+        <v>80</v>
+      </c>
+      <c r="C51">
+        <v>87</v>
+      </c>
+      <c r="D51" s="8">
+        <v>27.83</v>
+      </c>
+      <c r="E51" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F51" s="16">
+        <v>3.5525820000000001</v>
+      </c>
+      <c r="G51" s="7">
+        <v>8.7864000000000004</v>
+      </c>
+      <c r="H51" s="13">
+        <v>32.720821999999998</v>
+      </c>
+      <c r="I51" t="s">
+        <v>526</v>
+      </c>
+      <c r="J51" s="10">
+        <v>4.9099999999999998E-2</v>
+      </c>
+      <c r="K51" s="10">
+        <v>288</v>
+      </c>
+      <c r="L51" s="4">
+        <v>130.92400000000001</v>
+      </c>
+      <c r="M51">
+        <v>13.35</v>
+      </c>
+      <c r="N51">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>38</v>
+      </c>
+      <c r="B52" t="s">
+        <v>82</v>
+      </c>
+      <c r="C52">
+        <v>87</v>
+      </c>
+      <c r="D52" s="8">
+        <v>7</v>
+      </c>
+      <c r="E52" s="19" t="s">
+        <v>553</v>
+      </c>
+      <c r="F52" s="16">
+        <v>-1.2090236000000001</v>
+      </c>
+      <c r="G52" s="7">
+        <v>-1.1639375999999999</v>
+      </c>
+      <c r="H52" s="13">
+        <v>4.3334539999999997</v>
+      </c>
+      <c r="I52" t="s">
+        <v>527</v>
+      </c>
+      <c r="J52" s="10">
+        <v>1.9000000000000001E-4</v>
+      </c>
+      <c r="K52">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="L52" s="4">
+        <v>17.341000000000001</v>
+      </c>
+      <c r="M52">
+        <v>33.5</v>
+      </c>
+      <c r="N52">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>39</v>
+      </c>
+      <c r="B53" t="s">
+        <v>84</v>
+      </c>
+      <c r="C53">
+        <v>89</v>
+      </c>
+      <c r="D53" s="8">
+        <v>100</v>
+      </c>
+      <c r="E53" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F53" s="14">
+        <v>-0.23801048999999999</v>
+      </c>
+      <c r="G53" s="7">
+        <v>-1.3162791</v>
+      </c>
+      <c r="H53" s="14">
+        <v>4.9001979999999996</v>
+      </c>
+      <c r="I53" t="s">
+        <v>489</v>
+      </c>
+      <c r="J53" s="10">
+        <v>1.1900000000000001E-4</v>
+      </c>
+      <c r="K53">
+        <v>0.7</v>
+      </c>
+      <c r="L53" s="4">
+        <v>19.606999999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>40</v>
+      </c>
+      <c r="B54" t="s">
+        <v>87</v>
+      </c>
+      <c r="C54">
+        <v>91</v>
+      </c>
+      <c r="D54" s="8">
+        <v>11.22</v>
+      </c>
+      <c r="E54" s="19" t="s">
+        <v>549</v>
+      </c>
+      <c r="F54" s="16">
+        <v>-1.5424599999999999</v>
+      </c>
+      <c r="G54" s="7">
+        <v>-2.49743</v>
+      </c>
+      <c r="H54" s="13">
+        <v>9.2962980000000002</v>
+      </c>
+      <c r="I54" t="s">
+        <v>528</v>
+      </c>
+      <c r="J54" s="10">
+        <v>1.07E-3</v>
+      </c>
+      <c r="K54">
+        <v>6.26</v>
+      </c>
+      <c r="L54" s="4">
+        <v>37.197000000000003</v>
+      </c>
+      <c r="M54">
+        <v>-17.600000000000001</v>
+      </c>
+      <c r="N54">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>41</v>
+      </c>
+      <c r="B55" t="s">
+        <v>89</v>
+      </c>
+      <c r="C55">
+        <v>93</v>
+      </c>
+      <c r="D55" s="8">
+        <v>100</v>
+      </c>
+      <c r="E55" s="19" t="s">
+        <v>553</v>
+      </c>
+      <c r="F55" s="16">
+        <v>6.8216999999999999</v>
+      </c>
+      <c r="G55" s="7">
+        <v>6.5674000000000001</v>
+      </c>
+      <c r="H55" s="13">
+        <v>24.47617</v>
+      </c>
+      <c r="I55" t="s">
+        <v>529</v>
+      </c>
+      <c r="J55">
+        <v>0.48799999999999999</v>
+      </c>
+      <c r="K55" s="10">
+        <v>2870</v>
+      </c>
+      <c r="L55" s="4">
+        <v>97.936000000000007</v>
+      </c>
+      <c r="M55">
+        <v>-32</v>
+      </c>
+      <c r="N55">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>42</v>
+      </c>
+      <c r="B56" t="s">
+        <v>91</v>
+      </c>
+      <c r="C56">
+        <v>95</v>
+      </c>
+      <c r="D56" s="8">
+        <v>15.92</v>
+      </c>
+      <c r="E56" s="19" t="s">
+        <v>549</v>
+      </c>
+      <c r="F56" s="16">
+        <v>-1.0820000000000001</v>
+      </c>
+      <c r="G56" s="7">
+        <v>-1.7509999999999999</v>
+      </c>
+      <c r="H56" s="13">
+        <v>6.5169259999999998</v>
+      </c>
+      <c r="I56" t="s">
+        <v>530</v>
+      </c>
+      <c r="J56" s="10">
+        <v>5.2099999999999998E-4</v>
+      </c>
+      <c r="K56">
+        <v>3.06</v>
+      </c>
+      <c r="L56" s="4">
+        <v>26.076000000000001</v>
+      </c>
+      <c r="M56">
+        <v>-2.2000000000000002</v>
+      </c>
+      <c r="N56">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>42</v>
+      </c>
+      <c r="B57" t="s">
+        <v>91</v>
+      </c>
+      <c r="C57">
+        <v>97</v>
+      </c>
+      <c r="D57" s="8">
+        <v>9.5500000000000007</v>
+      </c>
+      <c r="E57" s="19" t="s">
+        <v>549</v>
+      </c>
+      <c r="F57" s="16">
+        <v>-1.105</v>
+      </c>
+      <c r="G57" s="7">
+        <v>-1.788</v>
+      </c>
+      <c r="H57" s="13">
+        <v>6.6536949999999999</v>
+      </c>
+      <c r="I57" t="s">
+        <v>530</v>
+      </c>
+      <c r="J57" s="10">
+        <v>3.3300000000000002E-4</v>
+      </c>
+      <c r="K57">
+        <v>1.95</v>
+      </c>
+      <c r="L57" s="4">
+        <v>26.623000000000001</v>
+      </c>
+      <c r="M57">
+        <v>25.5</v>
+      </c>
+      <c r="N57">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>44</v>
+      </c>
+      <c r="B58" t="s">
+        <v>95</v>
+      </c>
+      <c r="C58">
+        <v>99</v>
+      </c>
+      <c r="D58" s="8">
+        <v>12.76</v>
+      </c>
+      <c r="E58" s="19" t="s">
+        <v>549</v>
+      </c>
+      <c r="F58" s="16">
+        <v>-0.75880000000000003</v>
+      </c>
+      <c r="G58" s="7">
+        <v>-1.2290000000000001</v>
+      </c>
+      <c r="H58" s="13">
+        <v>4.6053689999999996</v>
+      </c>
+      <c r="I58" t="s">
+        <v>531</v>
+      </c>
+      <c r="J58" s="10">
+        <v>1.44E-4</v>
+      </c>
+      <c r="K58">
+        <v>0.84799999999999998</v>
+      </c>
+      <c r="L58" s="4">
+        <v>18.427</v>
+      </c>
+      <c r="M58">
+        <v>7.9</v>
+      </c>
+      <c r="N58">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>44</v>
+      </c>
+      <c r="B59" t="s">
+        <v>95</v>
+      </c>
+      <c r="C59">
+        <v>101</v>
+      </c>
+      <c r="D59" s="8">
+        <v>17.059999999999999</v>
+      </c>
+      <c r="E59" s="19" t="s">
+        <v>549</v>
+      </c>
+      <c r="F59" s="16">
+        <v>-0.85050000000000003</v>
+      </c>
+      <c r="G59" s="7">
+        <v>-1.377</v>
+      </c>
+      <c r="H59" s="13">
+        <v>5.1613259999999999</v>
+      </c>
+      <c r="I59" t="s">
+        <v>532</v>
+      </c>
+      <c r="J59" s="10">
+        <v>2.7099999999999997E-4</v>
+      </c>
+      <c r="K59">
+        <v>1.59</v>
+      </c>
+      <c r="L59" s="4">
+        <v>20.652000000000001</v>
+      </c>
+      <c r="M59">
+        <v>45.7</v>
+      </c>
+      <c r="N59">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>45</v>
+      </c>
+      <c r="B60" t="s">
+        <v>98</v>
+      </c>
+      <c r="C60">
+        <v>103</v>
+      </c>
+      <c r="D60" s="8">
+        <v>100</v>
+      </c>
+      <c r="E60" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F60" s="14">
+        <v>-0.15310000000000001</v>
+      </c>
+      <c r="G60" s="7">
+        <v>-0.8468</v>
+      </c>
+      <c r="H60" s="14">
+        <v>3.1864469999999998</v>
+      </c>
+      <c r="I60" t="s">
+        <v>490</v>
+      </c>
+      <c r="J60" s="10">
+        <v>3.1699999999999998E-5</v>
+      </c>
+      <c r="K60">
+        <v>0.186</v>
+      </c>
+      <c r="L60" s="4">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>46</v>
+      </c>
+      <c r="B61" t="s">
+        <v>101</v>
+      </c>
+      <c r="C61">
+        <v>105</v>
+      </c>
+      <c r="D61" s="8">
+        <v>22.33</v>
+      </c>
+      <c r="E61" s="19" t="s">
+        <v>549</v>
+      </c>
+      <c r="F61" s="16">
+        <v>-0.76</v>
+      </c>
+      <c r="G61" s="7">
+        <v>-1.23</v>
+      </c>
+      <c r="H61" s="13">
+        <v>4.5761000000000003</v>
+      </c>
+      <c r="I61" t="s">
+        <v>533</v>
+      </c>
+      <c r="J61" s="10">
+        <v>2.5300000000000002E-4</v>
+      </c>
+      <c r="K61">
+        <v>1.49</v>
+      </c>
+      <c r="L61" s="4">
+        <v>18.309999999999999</v>
+      </c>
+      <c r="M61">
+        <v>66</v>
+      </c>
+      <c r="N61">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>47</v>
+      </c>
+      <c r="B62" t="s">
+        <v>102</v>
+      </c>
+      <c r="C62">
+        <v>107</v>
+      </c>
+      <c r="D62" s="8">
+        <v>51.838999999999999</v>
+      </c>
+      <c r="E62" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F62" s="14">
+        <v>-0.19689893</v>
+      </c>
+      <c r="G62" s="7">
+        <v>-1.0889181000000001</v>
+      </c>
+      <c r="H62" s="14">
+        <v>4.0478189999999996</v>
+      </c>
+      <c r="I62" t="s">
+        <v>491</v>
+      </c>
+      <c r="J62" s="10">
+        <v>3.4999999999999997E-5</v>
+      </c>
+      <c r="K62">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="L62" s="4">
+        <v>16.196999999999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>47</v>
+      </c>
+      <c r="B63" t="s">
+        <v>102</v>
+      </c>
+      <c r="C63">
+        <v>109</v>
+      </c>
+      <c r="D63" s="8">
+        <v>48.161000000000001</v>
+      </c>
+      <c r="E63" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F63" s="14">
+        <v>-0.22636279000000001</v>
+      </c>
+      <c r="G63" s="7">
+        <v>-1.2518634</v>
+      </c>
+      <c r="H63" s="14">
+        <v>4.6535330000000004</v>
+      </c>
+      <c r="I63" t="s">
+        <v>491</v>
+      </c>
+      <c r="J63" s="10">
+        <v>4.9400000000000001E-5</v>
+      </c>
+      <c r="K63">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="L63" s="4">
+        <v>18.62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>48</v>
+      </c>
+      <c r="B64" t="s">
+        <v>104</v>
+      </c>
+      <c r="C64">
+        <v>111</v>
+      </c>
+      <c r="D64" s="8">
+        <v>12.8</v>
+      </c>
+      <c r="E64" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F64" s="14">
+        <v>-1.0303728999999999</v>
+      </c>
+      <c r="G64" s="7">
+        <v>-5.6983131</v>
+      </c>
+      <c r="H64" s="14">
+        <v>21.215479999999999</v>
+      </c>
+      <c r="I64" t="s">
+        <v>492</v>
+      </c>
+      <c r="J64" s="10">
+        <v>1.24E-3</v>
+      </c>
+      <c r="K64">
+        <v>7.27</v>
+      </c>
+      <c r="L64" s="4">
+        <v>84.89</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>48</v>
+      </c>
+      <c r="B65" t="s">
+        <v>104</v>
+      </c>
+      <c r="C65">
+        <v>113</v>
+      </c>
+      <c r="D65" s="8">
+        <v>12.22</v>
+      </c>
+      <c r="E65" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F65" s="14">
+        <v>-1.0778567999999999</v>
+      </c>
+      <c r="G65" s="7">
+        <v>-5.9609154999999996</v>
+      </c>
+      <c r="H65" s="14">
+        <v>22.193175</v>
+      </c>
+      <c r="I65" t="s">
+        <v>492</v>
+      </c>
+      <c r="J65" s="10">
+        <v>1.3500000000000001E-3</v>
+      </c>
+      <c r="K65">
+        <v>7.94</v>
+      </c>
+      <c r="L65" s="4">
+        <v>88.802000000000007</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>49</v>
+      </c>
+      <c r="B66" t="s">
+        <v>107</v>
+      </c>
+      <c r="C66">
+        <v>113</v>
+      </c>
+      <c r="D66" s="8">
+        <v>4.29</v>
+      </c>
+      <c r="E66" s="19" t="s">
+        <v>553</v>
+      </c>
+      <c r="F66" s="16">
+        <v>6.1124000000000001</v>
+      </c>
+      <c r="G66" s="7">
+        <v>5.8845000000000001</v>
+      </c>
+      <c r="H66" s="13">
+        <v>21.865755</v>
+      </c>
+      <c r="I66" t="s">
+        <v>534</v>
+      </c>
+      <c r="J66" s="10">
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="K66">
+        <v>88.5</v>
+      </c>
+      <c r="L66" s="4">
+        <v>87.491</v>
+      </c>
+      <c r="M66">
+        <v>79.900000000000006</v>
+      </c>
+      <c r="N66">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>49</v>
+      </c>
+      <c r="B67" t="s">
+        <v>107</v>
+      </c>
+      <c r="C67">
+        <v>115</v>
+      </c>
+      <c r="D67" s="8">
+        <v>95.71</v>
+      </c>
+      <c r="E67" s="19" t="s">
+        <v>553</v>
+      </c>
+      <c r="F67" s="16">
+        <v>6.1256000000000004</v>
+      </c>
+      <c r="G67" s="7">
+        <v>5.8971999999999998</v>
+      </c>
+      <c r="H67" s="13">
+        <v>21.912628999999999</v>
+      </c>
+      <c r="I67" t="s">
+        <v>534</v>
+      </c>
+      <c r="J67">
+        <v>0.33800000000000002</v>
+      </c>
+      <c r="K67" s="10">
+        <v>1990</v>
+      </c>
+      <c r="L67" s="4">
+        <v>87.679000000000002</v>
+      </c>
+      <c r="M67">
+        <v>81</v>
+      </c>
+      <c r="N67">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>50</v>
+      </c>
+      <c r="B68" t="s">
+        <v>108</v>
+      </c>
+      <c r="C68">
+        <v>115</v>
+      </c>
+      <c r="D68" s="8">
+        <v>0.34</v>
+      </c>
+      <c r="E68" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F68" s="14">
+        <v>-1.5914999999999999</v>
+      </c>
+      <c r="G68" s="7">
+        <v>-8.8012999999999995</v>
+      </c>
+      <c r="H68" s="14">
+        <v>32.718749000000003</v>
+      </c>
+      <c r="I68" t="s">
+        <v>493</v>
+      </c>
+      <c r="J68" s="10">
+        <v>1.21E-4</v>
+      </c>
+      <c r="K68">
+        <v>0.71099999999999997</v>
+      </c>
+      <c r="L68" s="4">
+        <v>130.91800000000001</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>50</v>
+      </c>
+      <c r="B69" t="s">
+        <v>108</v>
+      </c>
+      <c r="C69">
+        <v>117</v>
+      </c>
+      <c r="D69" s="8">
+        <v>7.68</v>
+      </c>
+      <c r="E69" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F69" s="14">
+        <v>-1.7338499999999999</v>
+      </c>
+      <c r="G69" s="7">
+        <v>-9.5887899999999995</v>
+      </c>
+      <c r="H69" s="14">
+        <v>35.632258999999998</v>
+      </c>
+      <c r="I69" t="s">
+        <v>493</v>
+      </c>
+      <c r="J69" s="10">
+        <v>3.5400000000000002E-3</v>
+      </c>
+      <c r="K69">
+        <v>20.8</v>
+      </c>
+      <c r="L69" s="4">
+        <v>142.57499999999999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>50</v>
+      </c>
+      <c r="B70" t="s">
+        <v>108</v>
+      </c>
+      <c r="C70">
+        <v>119</v>
+      </c>
+      <c r="D70" s="8">
+        <v>8.59</v>
+      </c>
+      <c r="E70" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F70" s="14">
+        <v>-1.8139400000000001</v>
+      </c>
+      <c r="G70" s="7">
+        <v>-10.031700000000001</v>
+      </c>
+      <c r="H70" s="14">
+        <v>37.290632000000002</v>
+      </c>
+      <c r="I70" t="s">
+        <v>493</v>
+      </c>
+      <c r="J70" s="10">
+        <v>4.5300000000000002E-3</v>
+      </c>
+      <c r="K70">
+        <v>26.6</v>
+      </c>
+      <c r="L70" s="4">
+        <v>149.21100000000001</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>51</v>
+      </c>
+      <c r="B71" t="s">
+        <v>109</v>
+      </c>
+      <c r="C71">
+        <v>121</v>
+      </c>
+      <c r="D71" s="8">
+        <v>57.21</v>
+      </c>
+      <c r="E71" s="19" t="s">
+        <v>549</v>
+      </c>
+      <c r="F71" s="16">
+        <v>3.9796</v>
+      </c>
+      <c r="G71" s="7">
+        <v>6.4435000000000002</v>
+      </c>
+      <c r="H71" s="13">
+        <v>23.930577</v>
+      </c>
+      <c r="I71" t="s">
+        <v>535</v>
+      </c>
+      <c r="J71" s="10">
+        <v>9.3299999999999994E-2</v>
+      </c>
+      <c r="K71" s="10">
+        <v>548</v>
+      </c>
+      <c r="L71" s="4">
+        <v>95.753</v>
+      </c>
+      <c r="M71">
+        <v>-36</v>
+      </c>
+      <c r="N71">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>51</v>
+      </c>
+      <c r="B72" t="s">
+        <v>109</v>
+      </c>
+      <c r="C72">
+        <v>123</v>
+      </c>
+      <c r="D72" s="8">
+        <v>42.79</v>
+      </c>
+      <c r="E72" s="19" t="s">
+        <v>551</v>
+      </c>
+      <c r="F72" s="16">
+        <v>2.8912</v>
+      </c>
+      <c r="G72" s="7">
+        <v>3.4891999999999999</v>
+      </c>
+      <c r="H72" s="13">
+        <v>12.959217000000001</v>
+      </c>
+      <c r="I72" t="s">
+        <v>535</v>
+      </c>
+      <c r="J72" s="10">
+        <v>1.9900000000000001E-2</v>
+      </c>
+      <c r="K72" s="10">
+        <v>117</v>
+      </c>
+      <c r="L72" s="4">
+        <v>51.853999999999999</v>
+      </c>
+      <c r="M72">
+        <v>-49</v>
+      </c>
+      <c r="N72">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>52</v>
+      </c>
+      <c r="B73" t="s">
+        <v>110</v>
+      </c>
+      <c r="C73">
+        <v>123</v>
+      </c>
+      <c r="D73" s="8">
+        <v>0.89</v>
+      </c>
+      <c r="E73" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F73" s="14">
+        <v>-1.2764310000000001</v>
+      </c>
+      <c r="G73" s="7">
+        <v>-7.0590979999999997</v>
+      </c>
+      <c r="H73" s="14">
+        <v>26.169741999999999</v>
+      </c>
+      <c r="I73" t="s">
+        <v>494</v>
+      </c>
+      <c r="J73" s="10">
+        <v>1.64E-4</v>
+      </c>
+      <c r="K73">
+        <v>0.96099999999999997</v>
+      </c>
+      <c r="L73" s="4">
+        <v>104.71299999999999</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>52</v>
+      </c>
+      <c r="B74" t="s">
+        <v>110</v>
+      </c>
+      <c r="C74">
+        <v>125</v>
+      </c>
+      <c r="D74" s="8">
+        <v>7.07</v>
+      </c>
+      <c r="E74" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F74" s="14">
+        <v>-1.5389360000000001</v>
+      </c>
+      <c r="G74" s="7">
+        <v>-8.5108403999999993</v>
+      </c>
+      <c r="H74" s="14">
+        <v>31.549769000000001</v>
+      </c>
+      <c r="I74" t="s">
+        <v>494</v>
+      </c>
+      <c r="J74" s="10">
+        <v>2.2799999999999999E-3</v>
+      </c>
+      <c r="K74">
+        <v>13.4</v>
+      </c>
+      <c r="L74" s="4">
+        <v>126.24</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>53</v>
+      </c>
+      <c r="B75" t="s">
+        <v>112</v>
+      </c>
+      <c r="C75">
+        <v>127</v>
+      </c>
+      <c r="D75" s="8">
+        <v>100</v>
+      </c>
+      <c r="E75" s="19" t="s">
+        <v>549</v>
+      </c>
+      <c r="F75" s="16">
+        <v>3.3287100000000001</v>
+      </c>
+      <c r="G75" s="7">
+        <v>5.3895730000000004</v>
+      </c>
+      <c r="H75" s="13">
+        <v>20.007486</v>
+      </c>
+      <c r="I75" t="s">
+        <v>536</v>
+      </c>
+      <c r="J75" s="10">
+        <v>9.5399999999999999E-2</v>
+      </c>
+      <c r="K75" s="10">
+        <v>560</v>
+      </c>
+      <c r="L75" s="4">
+        <v>80.055999999999997</v>
+      </c>
+      <c r="M75">
+        <v>-71</v>
+      </c>
+      <c r="N75">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>54</v>
+      </c>
+      <c r="B76" t="s">
+        <v>115</v>
+      </c>
+      <c r="C76">
+        <v>129</v>
+      </c>
+      <c r="D76" s="8">
+        <v>26.44</v>
+      </c>
+      <c r="E76" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F76" s="14">
+        <v>-1.347494</v>
+      </c>
+      <c r="G76" s="7">
+        <v>-7.4521030000000001</v>
+      </c>
+      <c r="H76" s="14">
+        <v>27.810186000000002</v>
+      </c>
+      <c r="I76" t="s">
+        <v>495</v>
+      </c>
+      <c r="J76" s="10">
+        <v>5.7200000000000003E-3</v>
+      </c>
+      <c r="K76">
+        <v>33.6</v>
+      </c>
+      <c r="L76" s="4">
+        <v>111.277</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>54</v>
+      </c>
+      <c r="B77" t="s">
+        <v>115</v>
+      </c>
+      <c r="C77">
+        <v>131</v>
+      </c>
+      <c r="D77" s="8">
+        <v>21.18</v>
+      </c>
+      <c r="E77" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F77" s="16">
+        <v>0.89318989999999998</v>
+      </c>
+      <c r="G77" s="7">
+        <v>2.209076</v>
+      </c>
+      <c r="H77" s="13">
+        <v>8.2439210000000003</v>
+      </c>
+      <c r="I77" t="s">
+        <v>495</v>
+      </c>
+      <c r="J77" s="10">
+        <v>5.9599999999999996E-4</v>
+      </c>
+      <c r="K77">
+        <v>3.5</v>
+      </c>
+      <c r="L77" s="4">
+        <v>32.985999999999997</v>
+      </c>
+      <c r="M77">
+        <v>-11.4</v>
+      </c>
+      <c r="N77">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>55</v>
+      </c>
+      <c r="B78" t="s">
+        <v>117</v>
+      </c>
+      <c r="C78">
+        <v>133</v>
+      </c>
+      <c r="D78" s="8">
+        <v>100</v>
+      </c>
+      <c r="E78" s="19" t="s">
+        <v>551</v>
+      </c>
+      <c r="F78" s="16">
+        <v>2.9277407000000002</v>
+      </c>
+      <c r="G78" s="7">
+        <v>3.5332539000000001</v>
+      </c>
+      <c r="H78" s="13">
+        <v>13.116142</v>
+      </c>
+      <c r="I78" t="s">
+        <v>537</v>
+      </c>
+      <c r="J78" s="10">
+        <v>4.8399999999999999E-2</v>
+      </c>
+      <c r="K78" s="10">
+        <v>284</v>
+      </c>
+      <c r="L78" s="4">
+        <v>52.481999999999999</v>
+      </c>
+      <c r="M78">
+        <v>-0.34300000000000003</v>
+      </c>
+      <c r="N78">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>56</v>
+      </c>
+      <c r="B79" t="s">
+        <v>119</v>
+      </c>
+      <c r="C79">
+        <v>135</v>
+      </c>
+      <c r="D79" s="8">
+        <v>6.5919999999999996</v>
+      </c>
+      <c r="E79" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F79" s="16">
+        <v>1.08178</v>
+      </c>
+      <c r="G79" s="7">
+        <v>2.6755</v>
+      </c>
+      <c r="H79" s="13">
+        <v>9.9344570000000001</v>
+      </c>
+      <c r="I79" t="s">
+        <v>538</v>
+      </c>
+      <c r="J79" s="10">
+        <v>3.3E-4</v>
+      </c>
+      <c r="K79">
+        <v>1.93</v>
+      </c>
+      <c r="L79" s="4">
+        <v>39.750999999999998</v>
+      </c>
+      <c r="M79">
+        <v>16</v>
+      </c>
+      <c r="N79">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>56</v>
+      </c>
+      <c r="B80" t="s">
+        <v>119</v>
+      </c>
+      <c r="C80">
+        <v>137</v>
+      </c>
+      <c r="D80" s="8">
+        <v>11.231999999999999</v>
+      </c>
+      <c r="E80" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F80" s="16">
+        <v>1.2101299999999999</v>
+      </c>
+      <c r="G80" s="7">
+        <v>2.99295</v>
+      </c>
+      <c r="H80" s="13">
+        <v>11.112928</v>
+      </c>
+      <c r="I80" t="s">
+        <v>538</v>
+      </c>
+      <c r="J80" s="10">
+        <v>7.8700000000000005E-4</v>
+      </c>
+      <c r="K80">
+        <v>4.62</v>
+      </c>
+      <c r="L80" s="4">
+        <v>44.466000000000001</v>
+      </c>
+      <c r="M80">
+        <v>24.5</v>
+      </c>
+      <c r="N80">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>57</v>
+      </c>
+      <c r="B81" t="s">
+        <v>120</v>
+      </c>
+      <c r="C81">
+        <v>138</v>
+      </c>
+      <c r="D81" s="8">
+        <v>0.09</v>
+      </c>
+      <c r="E81" s="19" t="s">
+        <v>554</v>
+      </c>
+      <c r="F81" s="16">
+        <v>4.0680949999999996</v>
+      </c>
+      <c r="G81" s="7">
+        <v>3.557239</v>
+      </c>
+      <c r="H81" s="13">
+        <v>13.1943</v>
+      </c>
+      <c r="I81" t="s">
+        <v>539</v>
+      </c>
+      <c r="J81" s="10">
+        <v>8.4599999999999996E-5</v>
+      </c>
+      <c r="K81">
+        <v>0.497</v>
+      </c>
+      <c r="L81" s="4">
+        <v>52.793999999999997</v>
+      </c>
+      <c r="M81">
+        <v>45</v>
+      </c>
+      <c r="N81">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>57</v>
+      </c>
+      <c r="B82" t="s">
+        <v>120</v>
+      </c>
+      <c r="C82">
+        <v>139</v>
+      </c>
+      <c r="D82" s="8">
+        <v>99.91</v>
+      </c>
+      <c r="E82" s="19" t="s">
+        <v>551</v>
+      </c>
+      <c r="F82" s="16">
+        <v>3.1556769999999998</v>
+      </c>
+      <c r="G82" s="7">
+        <v>3.8083317999999999</v>
+      </c>
+      <c r="H82" s="13">
+        <v>14.125641</v>
+      </c>
+      <c r="I82" t="s">
+        <v>539</v>
+      </c>
+      <c r="J82" s="10">
+        <v>6.0499999999999998E-2</v>
+      </c>
+      <c r="K82" s="10">
+        <v>356</v>
+      </c>
+      <c r="L82" s="4">
+        <v>56.521000000000001</v>
+      </c>
+      <c r="M82">
+        <v>20</v>
+      </c>
+      <c r="N82">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>59</v>
+      </c>
+      <c r="B83" t="s">
+        <v>124</v>
+      </c>
+      <c r="C83">
+        <v>141</v>
+      </c>
+      <c r="D83" s="8">
+        <v>100</v>
+      </c>
+      <c r="E83" s="19" t="s">
+        <v>549</v>
+      </c>
+      <c r="F83" s="16">
+        <v>5.0587</v>
+      </c>
+      <c r="G83" s="7">
+        <v>8.1906999999999996</v>
+      </c>
+      <c r="H83" s="13">
+        <v>30.62</v>
+      </c>
+      <c r="L83" s="4">
+        <v>122.51</v>
+      </c>
+      <c r="M83">
+        <v>-5.89</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>60</v>
+      </c>
+      <c r="B84" t="s">
+        <v>126</v>
+      </c>
+      <c r="C84">
+        <v>143</v>
+      </c>
+      <c r="D84" s="8">
+        <v>12.2</v>
+      </c>
+      <c r="E84" s="19" t="s">
+        <v>551</v>
+      </c>
+      <c r="F84" s="16">
+        <v>-1.208</v>
+      </c>
+      <c r="G84" s="7">
+        <v>-1.4570000000000001</v>
+      </c>
+      <c r="H84" s="13">
+        <v>5.45</v>
+      </c>
+      <c r="L84" s="4">
+        <v>21.8</v>
+      </c>
+      <c r="M84">
+        <v>-63</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>60</v>
+      </c>
+      <c r="B85" t="s">
+        <v>126</v>
+      </c>
+      <c r="C85">
+        <v>145</v>
+      </c>
+      <c r="D85" s="8">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E85" s="19" t="s">
+        <v>551</v>
+      </c>
+      <c r="F85" s="16">
+        <v>-0.74399999999999999</v>
+      </c>
+      <c r="G85" s="7">
+        <v>-0.89800000000000002</v>
+      </c>
+      <c r="H85" s="13">
+        <v>3.36</v>
+      </c>
+      <c r="L85" s="4">
+        <v>13.43</v>
+      </c>
+      <c r="M85">
+        <v>-33</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>62</v>
+      </c>
+      <c r="B86" t="s">
+        <v>131</v>
+      </c>
+      <c r="C86">
+        <v>147</v>
+      </c>
+      <c r="D86" s="8">
+        <v>14.99</v>
+      </c>
+      <c r="E86" s="19" t="s">
+        <v>551</v>
+      </c>
+      <c r="F86" s="16">
+        <v>-0.92390000000000005</v>
+      </c>
+      <c r="G86" s="7">
+        <v>-1.115</v>
+      </c>
+      <c r="H86" s="13">
+        <v>4.17</v>
+      </c>
+      <c r="L86" s="4">
+        <v>16.68</v>
+      </c>
+      <c r="M86">
+        <v>-25.9</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>62</v>
+      </c>
+      <c r="B87" t="s">
+        <v>131</v>
+      </c>
+      <c r="C87">
+        <v>149</v>
+      </c>
+      <c r="D87" s="8">
+        <v>13.82</v>
+      </c>
+      <c r="E87" s="19" t="s">
+        <v>551</v>
+      </c>
+      <c r="F87" s="16">
+        <v>-0.76160000000000005</v>
+      </c>
+      <c r="G87" s="7">
+        <v>-0.91920000000000002</v>
+      </c>
+      <c r="H87" s="13">
+        <v>3.44</v>
+      </c>
+      <c r="L87" s="4">
+        <v>13.75</v>
+      </c>
+      <c r="M87">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>63</v>
+      </c>
+      <c r="B88" t="s">
+        <v>134</v>
+      </c>
+      <c r="C88">
+        <v>151</v>
+      </c>
+      <c r="D88" s="8">
+        <v>47.81</v>
+      </c>
+      <c r="E88" s="19" t="s">
+        <v>549</v>
+      </c>
+      <c r="F88" s="16">
+        <v>4.1078000000000001</v>
+      </c>
+      <c r="G88" s="7">
+        <v>6.6509999999999998</v>
+      </c>
+      <c r="H88" s="13">
+        <v>24.86</v>
+      </c>
+      <c r="L88" s="4">
+        <v>99.48</v>
+      </c>
+      <c r="M88">
+        <v>90.3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>63</v>
+      </c>
+      <c r="B89" t="s">
+        <v>134</v>
+      </c>
+      <c r="C89">
+        <v>153</v>
+      </c>
+      <c r="D89" s="8">
+        <v>52.19</v>
+      </c>
+      <c r="E89" s="19" t="s">
+        <v>549</v>
+      </c>
+      <c r="F89" s="16">
+        <v>1.8139000000000001</v>
+      </c>
+      <c r="G89" s="7">
+        <v>2.9369000000000001</v>
+      </c>
+      <c r="H89" s="13">
+        <v>10.98</v>
+      </c>
+      <c r="L89" s="4">
+        <v>43.91</v>
+      </c>
+      <c r="M89">
+        <v>241.2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>64</v>
+      </c>
+      <c r="B90" t="s">
+        <v>137</v>
+      </c>
+      <c r="C90">
+        <v>155</v>
+      </c>
+      <c r="D90" s="8">
+        <v>14.8</v>
+      </c>
+      <c r="E90" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F90" s="16">
+        <v>-0.33207999999999999</v>
+      </c>
+      <c r="G90" s="7">
+        <v>-0.82132000000000005</v>
+      </c>
+      <c r="H90" s="13">
+        <v>3.07</v>
+      </c>
+      <c r="L90" s="4">
+        <v>12.28</v>
+      </c>
+      <c r="M90">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>64</v>
+      </c>
+      <c r="B91" t="s">
+        <v>137</v>
+      </c>
+      <c r="C91">
+        <v>157</v>
+      </c>
+      <c r="D91" s="8">
+        <v>15.65</v>
+      </c>
+      <c r="E91" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F91" s="16">
+        <v>-0.43540000000000001</v>
+      </c>
+      <c r="G91" s="7">
+        <v>-1.0769</v>
+      </c>
+      <c r="H91" s="13">
+        <v>4.03</v>
+      </c>
+      <c r="L91" s="4">
+        <v>16.11</v>
+      </c>
+      <c r="M91">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>65</v>
+      </c>
+      <c r="B92" t="s">
+        <v>140</v>
+      </c>
+      <c r="C92">
+        <v>159</v>
+      </c>
+      <c r="D92" s="8">
+        <v>100</v>
+      </c>
+      <c r="E92" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F92" s="16">
+        <v>2.6</v>
+      </c>
+      <c r="G92" s="7">
+        <v>6.431</v>
+      </c>
+      <c r="H92" s="13">
+        <v>24.04</v>
+      </c>
+      <c r="L92" s="4">
+        <v>96.18</v>
+      </c>
+      <c r="M92">
+        <v>143.19999999999999</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>66</v>
+      </c>
+      <c r="B93" t="s">
+        <v>142</v>
+      </c>
+      <c r="C93">
+        <v>161</v>
+      </c>
+      <c r="D93" s="8">
+        <v>18.91</v>
+      </c>
+      <c r="E93" s="19" t="s">
+        <v>549</v>
+      </c>
+      <c r="F93" s="16">
+        <v>-0.56830000000000003</v>
+      </c>
+      <c r="G93" s="7">
+        <v>-0.92010000000000003</v>
+      </c>
+      <c r="H93" s="13">
+        <v>3.44</v>
+      </c>
+      <c r="L93" s="4">
+        <v>13.75</v>
+      </c>
+      <c r="M93">
+        <v>250.7</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>66</v>
+      </c>
+      <c r="B94" t="s">
+        <v>142</v>
+      </c>
+      <c r="C94">
+        <v>161</v>
+      </c>
+      <c r="D94" s="8">
+        <v>24.9</v>
+      </c>
+      <c r="E94" s="19" t="s">
+        <v>549</v>
+      </c>
+      <c r="F94" s="16">
+        <v>0.79579999999999995</v>
+      </c>
+      <c r="G94" s="7">
+        <v>1.2889999999999999</v>
+      </c>
+      <c r="H94" s="13">
+        <v>4.82</v>
+      </c>
+      <c r="L94" s="4">
+        <v>19.28</v>
+      </c>
+      <c r="M94">
+        <v>264.8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>67</v>
+      </c>
+      <c r="B95" t="s">
+        <v>144</v>
+      </c>
+      <c r="C95">
+        <v>165</v>
+      </c>
+      <c r="D95" s="8">
+        <v>100</v>
+      </c>
+      <c r="E95" s="19" t="s">
+        <v>551</v>
+      </c>
+      <c r="F95" s="16">
+        <v>4.7320000000000002</v>
+      </c>
+      <c r="G95" s="7">
+        <v>5.71</v>
+      </c>
+      <c r="H95" s="13">
+        <v>21.34</v>
+      </c>
+      <c r="L95" s="4">
+        <v>84.57</v>
+      </c>
+      <c r="M95">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>68</v>
+      </c>
+      <c r="B96" t="s">
+        <v>146</v>
+      </c>
+      <c r="C96">
+        <v>167</v>
+      </c>
+      <c r="D96" s="8">
+        <v>22.93</v>
+      </c>
+      <c r="E96" s="19" t="s">
+        <v>551</v>
+      </c>
+      <c r="F96" s="16">
+        <v>-0.63934999999999997</v>
+      </c>
+      <c r="G96" s="7">
+        <v>-0.77156999999999998</v>
+      </c>
+      <c r="H96" s="13">
+        <v>2.88</v>
+      </c>
+      <c r="L96" s="4">
+        <v>11.54</v>
+      </c>
+      <c r="M96">
+        <v>356.5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>69</v>
+      </c>
+      <c r="B97" t="s">
+        <v>148</v>
+      </c>
+      <c r="C97">
+        <v>169</v>
+      </c>
+      <c r="D97" s="8">
+        <v>100</v>
+      </c>
+      <c r="E97" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F97" s="16">
+        <v>-0.40110000000000001</v>
+      </c>
+      <c r="G97" s="7">
+        <v>-2.218</v>
+      </c>
+      <c r="H97" s="13">
+        <v>8.2899999999999991</v>
+      </c>
+      <c r="L97" s="4">
+        <v>33.1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>70</v>
+      </c>
+      <c r="B98" t="s">
+        <v>151</v>
+      </c>
+      <c r="C98">
+        <v>171</v>
+      </c>
+      <c r="D98" s="8">
+        <v>14.28</v>
+      </c>
+      <c r="E98" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F98" s="16">
+        <v>0.85506000000000004</v>
+      </c>
+      <c r="G98" s="7">
+        <v>4.7287999999999997</v>
+      </c>
+      <c r="H98" s="13">
+        <v>17.499306000000001</v>
+      </c>
+      <c r="L98" s="4">
+        <v>70.02</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>70</v>
+      </c>
+      <c r="B99" t="s">
+        <v>151</v>
+      </c>
+      <c r="C99">
+        <v>173</v>
+      </c>
+      <c r="D99" s="8">
+        <v>16.13</v>
+      </c>
+      <c r="E99" s="19" t="s">
+        <v>549</v>
+      </c>
+      <c r="F99" s="16">
+        <v>-0.80445999999999995</v>
+      </c>
+      <c r="G99" s="7">
+        <v>-1.3025</v>
+      </c>
+      <c r="H99" s="13">
+        <v>4.8209999999999997</v>
+      </c>
+      <c r="L99" s="4">
+        <v>19.48</v>
+      </c>
+      <c r="M99">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>71</v>
+      </c>
+      <c r="B100" t="s">
+        <v>154</v>
+      </c>
+      <c r="C100">
+        <v>175</v>
+      </c>
+      <c r="D100" s="8">
+        <v>97.41</v>
+      </c>
+      <c r="E100" s="19" t="s">
+        <v>551</v>
+      </c>
+      <c r="F100" s="16">
+        <v>2.5316000000000001</v>
+      </c>
+      <c r="G100" s="7">
+        <v>3.0552000000000001</v>
+      </c>
+      <c r="H100" s="13">
+        <v>11.404</v>
+      </c>
+      <c r="L100" s="4">
+        <v>45.69</v>
+      </c>
+      <c r="M100">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>71</v>
+      </c>
+      <c r="B101" t="s">
+        <v>154</v>
+      </c>
+      <c r="C101">
+        <v>176</v>
+      </c>
+      <c r="D101" s="8">
+        <v>2.59</v>
+      </c>
+      <c r="E101" s="19" t="s">
+        <v>555</v>
+      </c>
+      <c r="F101" s="16">
+        <v>3.3879999999999999</v>
+      </c>
+      <c r="G101" s="7">
+        <v>2.1684000000000001</v>
+      </c>
+      <c r="H101" s="13">
+        <v>8.1310000000000002</v>
+      </c>
+      <c r="L101" s="4">
+        <v>32.43</v>
+      </c>
+      <c r="M101">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>72</v>
+      </c>
+      <c r="B102" t="s">
+        <v>157</v>
+      </c>
+      <c r="C102">
+        <v>177</v>
+      </c>
+      <c r="D102" s="8">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="E102" s="19" t="s">
+        <v>551</v>
+      </c>
+      <c r="F102" s="16">
+        <v>0.89970000000000006</v>
+      </c>
+      <c r="G102" s="7">
+        <v>1.0860000000000001</v>
+      </c>
+      <c r="H102" s="13">
+        <v>4.0069999999999997</v>
+      </c>
+      <c r="I102" t="s">
+        <v>540</v>
+      </c>
+      <c r="J102" s="10">
+        <v>2.61E-4</v>
+      </c>
+      <c r="K102">
+        <v>1.54</v>
+      </c>
+      <c r="L102" s="4">
+        <v>16.239999999999998</v>
+      </c>
+      <c r="M102">
+        <v>336.5</v>
+      </c>
+      <c r="N102" s="10">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>72</v>
+      </c>
+      <c r="B103" t="s">
+        <v>157</v>
+      </c>
+      <c r="C103">
+        <v>179</v>
+      </c>
+      <c r="D103" s="8">
+        <v>13.62</v>
+      </c>
+      <c r="E103" s="19" t="s">
+        <v>553</v>
+      </c>
+      <c r="F103" s="16">
+        <v>-0.70850000000000002</v>
+      </c>
+      <c r="G103" s="7">
+        <v>-0.68210000000000004</v>
+      </c>
+      <c r="H103" s="13">
+        <v>2.5169999999999999</v>
+      </c>
+      <c r="I103" t="s">
+        <v>540</v>
+      </c>
+      <c r="J103" s="10">
+        <v>7.4499999999999995E-5</v>
+      </c>
+      <c r="K103">
+        <v>0.438</v>
+      </c>
+      <c r="L103" s="4">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="M103">
+        <v>379.3</v>
+      </c>
+      <c r="N103" s="10">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>73</v>
+      </c>
+      <c r="B104" t="s">
+        <v>158</v>
+      </c>
+      <c r="C104">
+        <v>181</v>
+      </c>
+      <c r="D104" s="8">
+        <v>99.988</v>
+      </c>
+      <c r="E104" s="19" t="s">
+        <v>551</v>
+      </c>
+      <c r="F104" s="16">
+        <v>2.6879</v>
+      </c>
+      <c r="G104" s="7">
+        <v>3.2437999999999998</v>
+      </c>
+      <c r="H104" s="13">
+        <v>11.989599999999999</v>
+      </c>
+      <c r="I104" t="s">
+        <v>541</v>
+      </c>
+      <c r="J104" s="10">
+        <v>3.7400000000000003E-2</v>
+      </c>
+      <c r="K104" s="10">
+        <v>220</v>
+      </c>
+      <c r="L104" s="4">
+        <v>47.973999999999997</v>
+      </c>
+      <c r="M104">
+        <v>317</v>
+      </c>
+      <c r="N104" s="10">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>74</v>
+      </c>
+      <c r="B105" t="s">
+        <v>161</v>
+      </c>
+      <c r="C105">
+        <v>183</v>
+      </c>
+      <c r="D105" s="8">
+        <v>14.31</v>
+      </c>
+      <c r="E105" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F105" s="14">
+        <v>0.20400919000000001</v>
+      </c>
+      <c r="G105" s="7">
+        <v>1.1282403000000001</v>
+      </c>
+      <c r="H105" s="14">
+        <v>4.1663870000000003</v>
+      </c>
+      <c r="I105" t="s">
+        <v>496</v>
+      </c>
+      <c r="J105" s="10">
+        <v>1.0699999999999999E-5</v>
+      </c>
+      <c r="K105" s="10">
+        <v>6.3100000000000003E-2</v>
+      </c>
+      <c r="L105" s="4">
+        <v>16.670999999999999</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>75</v>
+      </c>
+      <c r="B106" t="s">
+        <v>163</v>
+      </c>
+      <c r="C106">
+        <v>185</v>
+      </c>
+      <c r="D106" s="8">
+        <v>37.4</v>
+      </c>
+      <c r="E106" s="19" t="s">
+        <v>549</v>
+      </c>
+      <c r="F106" s="16">
+        <v>3.7709999999999999</v>
+      </c>
+      <c r="G106" s="7">
+        <v>6.1056999999999997</v>
+      </c>
+      <c r="H106" s="13">
+        <v>22.5246</v>
+      </c>
+      <c r="I106" t="s">
+        <v>542</v>
+      </c>
+      <c r="J106" s="10">
+        <v>5.1900000000000002E-2</v>
+      </c>
+      <c r="K106" s="10">
+        <v>305</v>
+      </c>
+      <c r="L106" s="4">
+        <v>90.128</v>
+      </c>
+      <c r="M106">
+        <v>218</v>
+      </c>
+      <c r="N106" s="10">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>75</v>
+      </c>
+      <c r="B107" t="s">
+        <v>163</v>
+      </c>
+      <c r="C107">
+        <v>187</v>
+      </c>
+      <c r="D107" s="8">
+        <v>62.6</v>
+      </c>
+      <c r="E107" s="19" t="s">
+        <v>549</v>
+      </c>
+      <c r="F107" s="16">
+        <v>3.8096000000000001</v>
+      </c>
+      <c r="G107" s="7">
+        <v>6.1681999999999997</v>
+      </c>
+      <c r="H107" s="13">
+        <v>22.7516</v>
+      </c>
+      <c r="I107" t="s">
+        <v>542</v>
+      </c>
+      <c r="J107" s="10">
+        <v>8.9499999999999996E-2</v>
+      </c>
+      <c r="K107" s="10">
+        <v>526</v>
+      </c>
+      <c r="L107" s="4">
+        <v>91.036000000000001</v>
+      </c>
+      <c r="M107">
+        <v>207</v>
+      </c>
+      <c r="N107" s="10">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>76</v>
+      </c>
+      <c r="B108" t="s">
+        <v>165</v>
+      </c>
+      <c r="C108">
+        <v>187</v>
+      </c>
+      <c r="D108" s="8">
+        <v>1.96</v>
+      </c>
+      <c r="E108" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F108" s="14">
+        <v>0.11198039999999999</v>
+      </c>
+      <c r="G108" s="7">
+        <v>0.61928950000000005</v>
+      </c>
+      <c r="H108" s="14">
+        <v>2.2823310000000001</v>
+      </c>
+      <c r="I108" t="s">
+        <v>497</v>
+      </c>
+      <c r="J108" s="10">
+        <v>2.4299999999999999E-7</v>
+      </c>
+      <c r="K108" s="10">
+        <v>1.4300000000000001E-3</v>
+      </c>
+      <c r="L108" s="4">
+        <v>9.1319999999999997</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>76</v>
+      </c>
+      <c r="B109" t="s">
+        <v>165</v>
+      </c>
+      <c r="C109">
+        <v>189</v>
+      </c>
+      <c r="D109" s="8">
+        <v>16.149999999999999</v>
+      </c>
+      <c r="E109" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F109" s="16">
+        <v>0.85197000000000001</v>
+      </c>
+      <c r="G109" s="7">
+        <v>2.1071300000000002</v>
+      </c>
+      <c r="H109" s="13">
+        <v>7.7653999999999996</v>
+      </c>
+      <c r="I109" t="s">
+        <v>497</v>
+      </c>
+      <c r="J109" s="10">
+        <v>3.9500000000000001E-4</v>
+      </c>
+      <c r="K109">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="L109" s="4">
+        <v>31.071999999999999</v>
+      </c>
+      <c r="M109">
+        <v>85.6</v>
+      </c>
+      <c r="N109">
+        <v>9800</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>77</v>
+      </c>
+      <c r="B110" t="s">
+        <v>168</v>
+      </c>
+      <c r="C110">
+        <v>191</v>
+      </c>
+      <c r="D110" s="8">
+        <v>37.299999999999997</v>
+      </c>
+      <c r="E110" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F110" s="16">
+        <v>0.1946</v>
+      </c>
+      <c r="G110" s="7">
+        <v>0.48120000000000002</v>
+      </c>
+      <c r="H110" s="13">
+        <v>1.718</v>
+      </c>
+      <c r="I110" t="s">
+        <v>540</v>
+      </c>
+      <c r="J110" s="10">
+        <v>1.0900000000000001E-5</v>
+      </c>
+      <c r="K110" s="10">
+        <v>6.3799999999999996E-2</v>
+      </c>
+      <c r="L110" s="4">
+        <v>7.2</v>
+      </c>
+      <c r="M110">
+        <v>81.599999999999994</v>
+      </c>
+      <c r="N110">
+        <v>8900</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>77</v>
+      </c>
+      <c r="B111" t="s">
+        <v>502</v>
+      </c>
+      <c r="C111">
+        <v>193</v>
+      </c>
+      <c r="D111" s="8">
+        <v>62.7</v>
+      </c>
+      <c r="E111" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F111" s="16">
+        <v>0.21129999999999999</v>
+      </c>
+      <c r="G111" s="7">
+        <v>0.52270000000000005</v>
+      </c>
+      <c r="H111" s="13">
+        <v>1.871</v>
+      </c>
+      <c r="I111" t="s">
+        <v>540</v>
+      </c>
+      <c r="J111" s="10">
+        <v>2.34E-5</v>
+      </c>
+      <c r="K111">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="L111" s="4">
+        <v>7.82</v>
+      </c>
+      <c r="M111">
+        <v>75.099999999999994</v>
+      </c>
+      <c r="N111">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>78</v>
+      </c>
+      <c r="B112" t="s">
+        <v>169</v>
+      </c>
+      <c r="C112">
+        <v>195</v>
+      </c>
+      <c r="D112" s="8">
+        <v>33.832000000000001</v>
+      </c>
+      <c r="E112" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F112" s="14">
+        <v>1.0557000000000001</v>
+      </c>
+      <c r="G112" s="7">
+        <v>5.8384999999999998</v>
+      </c>
+      <c r="H112" s="14">
+        <v>21.496784000000002</v>
+      </c>
+      <c r="I112" t="s">
+        <v>498</v>
+      </c>
+      <c r="J112" s="10">
+        <v>3.5100000000000001E-3</v>
+      </c>
+      <c r="K112">
+        <v>20.7</v>
+      </c>
+      <c r="L112" s="4">
+        <v>86.015000000000001</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>79</v>
+      </c>
+      <c r="B113" t="s">
+        <v>172</v>
+      </c>
+      <c r="C113">
+        <v>197</v>
+      </c>
+      <c r="D113" s="8">
+        <v>100</v>
+      </c>
+      <c r="E113" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F113" s="16">
+        <v>0.191271</v>
+      </c>
+      <c r="G113" s="7">
+        <v>0.47305999999999998</v>
+      </c>
+      <c r="H113" s="13">
+        <v>1.7290000000000001</v>
+      </c>
+      <c r="I113" t="s">
+        <v>540</v>
+      </c>
+      <c r="J113" s="10">
+        <v>2.7699999999999999E-5</v>
+      </c>
+      <c r="K113">
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="L113" s="4">
+        <v>7.08</v>
+      </c>
+      <c r="M113">
+        <v>54.7</v>
+      </c>
+      <c r="N113">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>80</v>
+      </c>
+      <c r="B114" t="s">
+        <v>173</v>
+      </c>
+      <c r="C114">
+        <v>199</v>
+      </c>
+      <c r="D114" s="8">
+        <v>16.87</v>
+      </c>
+      <c r="E114" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F114" s="14">
+        <v>0.87621937000000005</v>
+      </c>
+      <c r="G114" s="7">
+        <v>4.8457916000000001</v>
+      </c>
+      <c r="H114" s="14">
+        <v>17.910822</v>
+      </c>
+      <c r="I114" t="s">
+        <v>499</v>
+      </c>
+      <c r="J114" s="10">
+        <v>1E-3</v>
+      </c>
+      <c r="K114">
+        <v>5.89</v>
+      </c>
+      <c r="L114" s="4">
+        <v>71.667000000000002</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>80</v>
+      </c>
+      <c r="B115" t="s">
+        <v>173</v>
+      </c>
+      <c r="C115">
+        <v>201</v>
+      </c>
+      <c r="D115" s="8">
+        <v>13.18</v>
+      </c>
+      <c r="E115" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="F115" s="16">
+        <v>-0.72324829999999996</v>
+      </c>
+      <c r="G115" s="7">
+        <v>-1.7887690000000001</v>
+      </c>
+      <c r="H115" s="13">
+        <v>6.6115830000000004</v>
+      </c>
+      <c r="I115" t="s">
+        <v>499</v>
+      </c>
+      <c r="J115" s="10">
+        <v>1.9699999999999999E-4</v>
+      </c>
+      <c r="K115">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="L115" s="4">
+        <v>26.454999999999998</v>
+      </c>
+      <c r="M115">
+        <v>38.6</v>
+      </c>
+      <c r="N115">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>81</v>
+      </c>
+      <c r="B116" t="s">
+        <v>175</v>
+      </c>
+      <c r="C116">
+        <v>203</v>
+      </c>
+      <c r="D116" s="8">
+        <v>29.524000000000001</v>
+      </c>
+      <c r="E116" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F116" s="14">
+        <v>2.8098330499999999</v>
+      </c>
+      <c r="G116" s="7">
+        <v>15.5393338</v>
+      </c>
+      <c r="H116" s="14">
+        <v>57.123199999999997</v>
+      </c>
+      <c r="I116" t="s">
+        <v>500</v>
+      </c>
+      <c r="J116" s="10">
+        <v>5.79E-2</v>
+      </c>
+      <c r="K116" s="10">
+        <v>340</v>
+      </c>
+      <c r="L116" s="4">
+        <v>228.56700000000001</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>81</v>
+      </c>
+      <c r="B117" t="s">
+        <v>175</v>
+      </c>
+      <c r="C117">
+        <v>205</v>
+      </c>
+      <c r="D117" s="8">
+        <v>70.475999999999999</v>
+      </c>
+      <c r="E117" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F117" s="14">
+        <v>2.8374709400000002</v>
+      </c>
+      <c r="G117" s="7">
+        <v>15.692180799999999</v>
+      </c>
+      <c r="H117" s="14">
+        <v>57.683838000000002</v>
+      </c>
+      <c r="I117" t="s">
+        <v>500</v>
+      </c>
+      <c r="J117" s="10">
+        <v>0.14199999999999999</v>
+      </c>
+      <c r="K117" s="10">
+        <v>836</v>
+      </c>
+      <c r="L117" s="4">
+        <v>230.81</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>82</v>
+      </c>
+      <c r="B118" t="s">
+        <v>177</v>
+      </c>
+      <c r="C118">
+        <v>207</v>
+      </c>
+      <c r="D118" s="8">
+        <v>22.1</v>
+      </c>
+      <c r="E118" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="F118" s="14">
+        <v>1.0090600000000001</v>
+      </c>
+      <c r="G118" s="7">
+        <v>5.5804600000000004</v>
+      </c>
+      <c r="H118" s="14">
+        <v>20.920598999999999</v>
+      </c>
+      <c r="I118" t="s">
+        <v>501</v>
+      </c>
+      <c r="J118" s="10">
+        <v>2.0100000000000001E-3</v>
+      </c>
+      <c r="K118">
+        <v>11.8</v>
+      </c>
+      <c r="L118" s="4">
+        <v>83.71</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>83</v>
+      </c>
+      <c r="B119" t="s">
+        <v>179</v>
+      </c>
+      <c r="C119">
+        <v>209</v>
+      </c>
+      <c r="D119" s="8">
+        <v>100</v>
+      </c>
+      <c r="E119" s="19" t="s">
+        <v>553</v>
+      </c>
+      <c r="F119" s="16">
+        <v>4.5444000000000004</v>
+      </c>
+      <c r="G119" s="7">
+        <v>4.375</v>
+      </c>
+      <c r="H119" s="13">
+        <v>16.069288</v>
+      </c>
+      <c r="I119" t="s">
+        <v>543</v>
+      </c>
+      <c r="J119" s="10">
+        <v>0.14399999999999999</v>
+      </c>
+      <c r="K119" s="10">
+        <v>848</v>
+      </c>
+      <c r="L119" s="4">
+        <v>64.298000000000002</v>
+      </c>
+      <c r="M119">
+        <v>-51.6</v>
+      </c>
+      <c r="N119">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>92</v>
+      </c>
+      <c r="B120" t="s">
+        <v>202</v>
+      </c>
+      <c r="C120">
+        <v>235</v>
+      </c>
+      <c r="D120" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="E120" s="19" t="s">
+        <v>551</v>
+      </c>
+      <c r="F120" s="16">
+        <v>-0.43</v>
+      </c>
+      <c r="G120" s="7">
+        <v>-0.52</v>
+      </c>
+      <c r="H120" s="13">
+        <v>1.8413999999999999</v>
+      </c>
+      <c r="L120" s="4">
+        <v>7.3680000000000003</v>
+      </c>
+      <c r="M120">
+        <v>493.6</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N120">
+    <sortCondition ref="A1:A120"/>
+  </sortState>
+  <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>